--- a/arvedi_data.xlsx
+++ b/arvedi_data.xlsx
@@ -3997,7 +3997,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>D0144832</v>
+        <v>D0144830</v>
       </c>
       <c r="B125" t="str">
         <v>1.450</v>
@@ -4026,7 +4026,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>D0144830</v>
+        <v>D0144832</v>
       </c>
       <c r="B126" t="str">
         <v>1.450</v>
@@ -5041,22 +5041,22 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>D0146907</v>
+        <v>D0144821</v>
       </c>
       <c r="B161" t="str">
-        <v>1.475</v>
+        <v>1.450</v>
       </c>
       <c r="C161" t="str">
         <v>304DL</v>
       </c>
       <c r="D161" t="str">
-        <v>4.00</v>
+        <v>4.07</v>
       </c>
       <c r="E161" t="str">
-        <v>2000.000</v>
+        <v>1500.000</v>
       </c>
       <c r="F161" t="str">
-        <v>4000.000</v>
+        <v>3000.000</v>
       </c>
       <c r="G161" t="str">
         <v>SHEETS</v>
@@ -5070,22 +5070,22 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>D0144821</v>
+        <v>D0146907</v>
       </c>
       <c r="B162" t="str">
-        <v>1.450</v>
+        <v>1.475</v>
       </c>
       <c r="C162" t="str">
         <v>304DL</v>
       </c>
       <c r="D162" t="str">
-        <v>4.07</v>
+        <v>4.00</v>
       </c>
       <c r="E162" t="str">
-        <v>1500.000</v>
+        <v>2000.000</v>
       </c>
       <c r="F162" t="str">
-        <v>3000.000</v>
+        <v>4000.000</v>
       </c>
       <c r="G162" t="str">
         <v>SHEETS</v>
@@ -6317,10 +6317,10 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>D0146910</v>
+        <v>D0145959</v>
       </c>
       <c r="B205" t="str">
-        <v>1.445</v>
+        <v>790</v>
       </c>
       <c r="C205" t="str">
         <v>304DL</v>
@@ -6329,10 +6329,10 @@
         <v>4.00</v>
       </c>
       <c r="E205" t="str">
-        <v>2000.000</v>
+        <v>1250.000</v>
       </c>
       <c r="F205" t="str">
-        <v>4000.000</v>
+        <v>2500.000</v>
       </c>
       <c r="G205" t="str">
         <v>SHEETS</v>
@@ -6346,10 +6346,10 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>D0145959</v>
+        <v>D0146910</v>
       </c>
       <c r="B206" t="str">
-        <v>790</v>
+        <v>1.445</v>
       </c>
       <c r="C206" t="str">
         <v>304DL</v>
@@ -6358,10 +6358,10 @@
         <v>4.00</v>
       </c>
       <c r="E206" t="str">
-        <v>1250.000</v>
+        <v>2000.000</v>
       </c>
       <c r="F206" t="str">
-        <v>2500.000</v>
+        <v>4000.000</v>
       </c>
       <c r="G206" t="str">
         <v>SHEETS</v>
@@ -11276,10 +11276,10 @@
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>D0147250</v>
+        <v>D0144247</v>
       </c>
       <c r="B376" t="str">
-        <v>2.533</v>
+        <v>1.260</v>
       </c>
       <c r="C376" t="str">
         <v>304DL</v>
@@ -11288,27 +11288,27 @@
         <v>0.81</v>
       </c>
       <c r="E376" t="str">
-        <v>1277.000</v>
+        <v>1250.000</v>
       </c>
       <c r="F376" t="str">
-        <v>0.000</v>
+        <v>2500.000</v>
       </c>
       <c r="G376" t="str">
-        <v>COILS</v>
+        <v>BLANKS</v>
       </c>
       <c r="H376" t="str">
         <v>BA</v>
       </c>
       <c r="I376" t="str">
-        <v>2.250</v>
+        <v>2.750</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>D0144247</v>
+        <v>D0147250</v>
       </c>
       <c r="B377" t="str">
-        <v>1.260</v>
+        <v>2.533</v>
       </c>
       <c r="C377" t="str">
         <v>304DL</v>
@@ -11317,19 +11317,19 @@
         <v>0.81</v>
       </c>
       <c r="E377" t="str">
-        <v>1250.000</v>
+        <v>1277.000</v>
       </c>
       <c r="F377" t="str">
-        <v>2500.000</v>
+        <v>0.000</v>
       </c>
       <c r="G377" t="str">
-        <v>BLANKS</v>
+        <v>COILS</v>
       </c>
       <c r="H377" t="str">
         <v>BA</v>
       </c>
       <c r="I377" t="str">
-        <v>2.750</v>
+        <v>2.250</v>
       </c>
     </row>
     <row r="378">
@@ -12291,19 +12291,19 @@
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>D0147416</v>
+        <v>C0925423</v>
       </c>
       <c r="B411" t="str">
-        <v>3.624</v>
+        <v>285</v>
       </c>
       <c r="C411" t="str">
         <v>304DL</v>
       </c>
       <c r="D411" t="str">
-        <v>1.00</v>
+        <v>0.61</v>
       </c>
       <c r="E411" t="str">
-        <v>500.000</v>
+        <v>80.000</v>
       </c>
       <c r="F411" t="str">
         <v>0.000</v>
@@ -12315,24 +12315,24 @@
         <v>BA</v>
       </c>
       <c r="I411" t="str">
-        <v>2.350</v>
+        <v>2.550</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>C0925423</v>
+        <v>D0147416</v>
       </c>
       <c r="B412" t="str">
-        <v>285</v>
+        <v>3.624</v>
       </c>
       <c r="C412" t="str">
         <v>304DL</v>
       </c>
       <c r="D412" t="str">
-        <v>0.61</v>
+        <v>1.00</v>
       </c>
       <c r="E412" t="str">
-        <v>80.000</v>
+        <v>500.000</v>
       </c>
       <c r="F412" t="str">
         <v>0.000</v>
@@ -12344,7 +12344,7 @@
         <v>BA</v>
       </c>
       <c r="I412" t="str">
-        <v>2.550</v>
+        <v>2.350</v>
       </c>
     </row>
     <row r="413">
@@ -15858,7 +15858,7 @@
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>C0970429</v>
+        <v>C0970345</v>
       </c>
       <c r="B534" t="str">
         <v>550</v>
@@ -15867,7 +15867,7 @@
         <v>316L</v>
       </c>
       <c r="D534" t="str">
-        <v>0.39</v>
+        <v>0.51</v>
       </c>
       <c r="E534" t="str">
         <v>240.000</v>
@@ -15887,7 +15887,7 @@
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>C0970345</v>
+        <v>C0970429</v>
       </c>
       <c r="B535" t="str">
         <v>550</v>
@@ -15896,7 +15896,7 @@
         <v>316L</v>
       </c>
       <c r="D535" t="str">
-        <v>0.51</v>
+        <v>0.39</v>
       </c>
       <c r="E535" t="str">
         <v>240.000</v>
@@ -19599,19 +19599,19 @@
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>C0905834</v>
+        <v>D0145539</v>
       </c>
       <c r="B663" t="str">
-        <v>3.888</v>
+        <v>2.120</v>
       </c>
       <c r="C663" t="str">
         <v>301NR</v>
       </c>
       <c r="D663" t="str">
-        <v>2.86</v>
+        <v>0.79</v>
       </c>
       <c r="E663" t="str">
-        <v>240.000</v>
+        <v>1272.000</v>
       </c>
       <c r="F663" t="str">
         <v>0.000</v>
@@ -19623,24 +19623,24 @@
         <v>2B</v>
       </c>
       <c r="I663" t="str">
-        <v>2.550</v>
+        <v>2.250</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>D0145539</v>
+        <v>C0905834</v>
       </c>
       <c r="B664" t="str">
-        <v>2.120</v>
+        <v>3.888</v>
       </c>
       <c r="C664" t="str">
         <v>301NR</v>
       </c>
       <c r="D664" t="str">
-        <v>0.79</v>
+        <v>2.86</v>
       </c>
       <c r="E664" t="str">
-        <v>1272.000</v>
+        <v>240.000</v>
       </c>
       <c r="F664" t="str">
         <v>0.000</v>
@@ -19652,7 +19652,7 @@
         <v>2B</v>
       </c>
       <c r="I664" t="str">
-        <v>2.250</v>
+        <v>2.550</v>
       </c>
     </row>
     <row r="665">
@@ -20295,19 +20295,19 @@
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>D0146574</v>
+        <v>C0984567</v>
       </c>
       <c r="B687" t="str">
-        <v>3.000</v>
+        <v>655</v>
       </c>
       <c r="C687" t="str">
         <v>409LI</v>
       </c>
       <c r="D687" t="str">
-        <v>3.06</v>
+        <v>0.50</v>
       </c>
       <c r="E687" t="str">
-        <v>1520.000</v>
+        <v>200.000</v>
       </c>
       <c r="F687" t="str">
         <v>0.000</v>
@@ -20319,24 +20319,24 @@
         <v>2B</v>
       </c>
       <c r="I687" t="str">
-        <v>1.300</v>
+        <v>1.400</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>C0984567</v>
+        <v>D0146574</v>
       </c>
       <c r="B688" t="str">
-        <v>655</v>
+        <v>3.000</v>
       </c>
       <c r="C688" t="str">
         <v>409LI</v>
       </c>
       <c r="D688" t="str">
-        <v>0.50</v>
+        <v>3.06</v>
       </c>
       <c r="E688" t="str">
-        <v>200.000</v>
+        <v>1520.000</v>
       </c>
       <c r="F688" t="str">
         <v>0.000</v>
@@ -20348,7 +20348,7 @@
         <v>2B</v>
       </c>
       <c r="I688" t="str">
-        <v>1.400</v>
+        <v>1.300</v>
       </c>
     </row>
     <row r="689">
@@ -20643,19 +20643,19 @@
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>D0144405</v>
+        <v>C0995208</v>
       </c>
       <c r="B699" t="str">
-        <v>1.550</v>
+        <v>1.476</v>
       </c>
       <c r="C699" t="str">
         <v>409LI</v>
       </c>
       <c r="D699" t="str">
-        <v>0.98</v>
+        <v>0.71</v>
       </c>
       <c r="E699" t="str">
-        <v>100.000</v>
+        <v>250.000</v>
       </c>
       <c r="F699" t="str">
         <v>0.000</v>
@@ -20667,24 +20667,24 @@
         <v>2B</v>
       </c>
       <c r="I699" t="str">
-        <v>1.300</v>
+        <v>1.350</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>C0995208</v>
+        <v>D0144405</v>
       </c>
       <c r="B700" t="str">
-        <v>1.476</v>
+        <v>1.550</v>
       </c>
       <c r="C700" t="str">
         <v>409LI</v>
       </c>
       <c r="D700" t="str">
-        <v>0.71</v>
+        <v>0.98</v>
       </c>
       <c r="E700" t="str">
-        <v>250.000</v>
+        <v>100.000</v>
       </c>
       <c r="F700" t="str">
         <v>0.000</v>
@@ -20696,7 +20696,7 @@
         <v>2B</v>
       </c>
       <c r="I700" t="str">
-        <v>1.350</v>
+        <v>1.300</v>
       </c>
     </row>
     <row r="701">
@@ -24674,10 +24674,10 @@
     </row>
     <row r="838">
       <c r="A838" t="str">
-        <v>C0984604</v>
+        <v>C0967875</v>
       </c>
       <c r="B838" t="str">
-        <v>1.117</v>
+        <v>1.273</v>
       </c>
       <c r="C838" t="str">
         <v>444NB</v>
@@ -24686,7 +24686,7 @@
         <v>1.50</v>
       </c>
       <c r="E838" t="str">
-        <v>150.000</v>
+        <v>145.000</v>
       </c>
       <c r="F838" t="str">
         <v>0.000</v>
@@ -24703,10 +24703,10 @@
     </row>
     <row r="839">
       <c r="A839" t="str">
-        <v>C0967875</v>
+        <v>C0984604</v>
       </c>
       <c r="B839" t="str">
-        <v>1.273</v>
+        <v>1.117</v>
       </c>
       <c r="C839" t="str">
         <v>444NB</v>
@@ -24715,7 +24715,7 @@
         <v>1.50</v>
       </c>
       <c r="E839" t="str">
-        <v>145.000</v>
+        <v>150.000</v>
       </c>
       <c r="F839" t="str">
         <v>0.000</v>
@@ -26269,19 +26269,19 @@
     </row>
     <row r="893">
       <c r="A893" t="str">
-        <v>C0984684</v>
+        <v>C0995195</v>
       </c>
       <c r="B893" t="str">
-        <v>947</v>
+        <v>559</v>
       </c>
       <c r="C893" t="str">
         <v>439M</v>
       </c>
       <c r="D893" t="str">
-        <v>0.61</v>
+        <v>0.81</v>
       </c>
       <c r="E893" t="str">
-        <v>280.000</v>
+        <v>220.000</v>
       </c>
       <c r="F893" t="str">
         <v>0.000</v>
@@ -26298,19 +26298,19 @@
     </row>
     <row r="894">
       <c r="A894" t="str">
-        <v>C0995195</v>
+        <v>C0984684</v>
       </c>
       <c r="B894" t="str">
-        <v>559</v>
+        <v>947</v>
       </c>
       <c r="C894" t="str">
         <v>439M</v>
       </c>
       <c r="D894" t="str">
-        <v>0.81</v>
+        <v>0.61</v>
       </c>
       <c r="E894" t="str">
-        <v>220.000</v>
+        <v>280.000</v>
       </c>
       <c r="F894" t="str">
         <v>0.000</v>
@@ -28038,10 +28038,10 @@
     </row>
     <row r="954">
       <c r="A954" t="str">
-        <v>C0949117</v>
+        <v>C0991091</v>
       </c>
       <c r="B954" t="str">
-        <v>228</v>
+        <v>256</v>
       </c>
       <c r="C954" t="str">
         <v>439M</v>
@@ -28067,10 +28067,10 @@
     </row>
     <row r="955">
       <c r="A955" t="str">
-        <v>C0991091</v>
+        <v>C0949117</v>
       </c>
       <c r="B955" t="str">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="C955" t="str">
         <v>439M</v>
@@ -30358,19 +30358,19 @@
     </row>
     <row r="1034">
       <c r="A1034" t="str">
-        <v>D0146354</v>
+        <v>C0991713</v>
       </c>
       <c r="B1034" t="str">
-        <v>3.358</v>
+        <v>1.070</v>
       </c>
       <c r="C1034" t="str">
         <v>441AR</v>
       </c>
       <c r="D1034" t="str">
-        <v>0.51</v>
+        <v>0.61</v>
       </c>
       <c r="E1034" t="str">
-        <v>220.000</v>
+        <v>300.000</v>
       </c>
       <c r="F1034" t="str">
         <v>0.000</v>
@@ -30382,24 +30382,24 @@
         <v>2B</v>
       </c>
       <c r="I1034" t="str">
-        <v>1.650</v>
+        <v>1.600</v>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="str">
-        <v>C0991713</v>
+        <v>D0146354</v>
       </c>
       <c r="B1035" t="str">
-        <v>1.070</v>
+        <v>3.358</v>
       </c>
       <c r="C1035" t="str">
         <v>441AR</v>
       </c>
       <c r="D1035" t="str">
-        <v>0.61</v>
+        <v>0.51</v>
       </c>
       <c r="E1035" t="str">
-        <v>300.000</v>
+        <v>220.000</v>
       </c>
       <c r="F1035" t="str">
         <v>0.000</v>
@@ -30411,7 +30411,7 @@
         <v>2B</v>
       </c>
       <c r="I1035" t="str">
-        <v>1.600</v>
+        <v>1.650</v>
       </c>
     </row>
     <row r="1036">
@@ -30677,19 +30677,19 @@
     </row>
     <row r="1045">
       <c r="A1045" t="str">
-        <v>D0137215</v>
+        <v>C0967898</v>
       </c>
       <c r="B1045" t="str">
-        <v>830</v>
+        <v>459</v>
       </c>
       <c r="C1045" t="str">
         <v>441AR</v>
       </c>
       <c r="D1045" t="str">
-        <v>0.97</v>
+        <v>0.51</v>
       </c>
       <c r="E1045" t="str">
-        <v>150.000</v>
+        <v>160.000</v>
       </c>
       <c r="F1045" t="str">
         <v>0.000</v>
@@ -30701,24 +30701,24 @@
         <v>2B</v>
       </c>
       <c r="I1045" t="str">
-        <v>1.550</v>
+        <v>1.650</v>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="str">
-        <v>C0967898</v>
+        <v>D0137215</v>
       </c>
       <c r="B1046" t="str">
-        <v>459</v>
+        <v>830</v>
       </c>
       <c r="C1046" t="str">
         <v>441AR</v>
       </c>
       <c r="D1046" t="str">
-        <v>0.51</v>
+        <v>0.97</v>
       </c>
       <c r="E1046" t="str">
-        <v>160.000</v>
+        <v>150.000</v>
       </c>
       <c r="F1046" t="str">
         <v>0.000</v>
@@ -30730,7 +30730,7 @@
         <v>2B</v>
       </c>
       <c r="I1046" t="str">
-        <v>1.650</v>
+        <v>1.550</v>
       </c>
     </row>
     <row r="1047">
@@ -31344,19 +31344,19 @@
     </row>
     <row r="1068">
       <c r="A1068" t="str">
-        <v>D0140543</v>
+        <v>D0142742</v>
       </c>
       <c r="B1068" t="str">
-        <v>269</v>
+        <v>433</v>
       </c>
       <c r="C1068" t="str">
         <v>441AR</v>
       </c>
       <c r="D1068" t="str">
-        <v>0.81</v>
+        <v>0.77</v>
       </c>
       <c r="E1068" t="str">
-        <v>120.000</v>
+        <v>215.000</v>
       </c>
       <c r="F1068" t="str">
         <v>0.000</v>
@@ -31373,19 +31373,19 @@
     </row>
     <row r="1069">
       <c r="A1069" t="str">
-        <v>D0142742</v>
+        <v>D0140543</v>
       </c>
       <c r="B1069" t="str">
-        <v>433</v>
+        <v>269</v>
       </c>
       <c r="C1069" t="str">
         <v>441AR</v>
       </c>
       <c r="D1069" t="str">
-        <v>0.77</v>
+        <v>0.81</v>
       </c>
       <c r="E1069" t="str">
-        <v>215.000</v>
+        <v>120.000</v>
       </c>
       <c r="F1069" t="str">
         <v>0.000</v>
@@ -32823,60 +32823,60 @@
     </row>
     <row r="1119">
       <c r="A1119" t="str">
-        <v>C0897501</v>
+        <v>D0144751</v>
       </c>
       <c r="B1119" t="str">
-        <v>323</v>
+        <v>1.790</v>
       </c>
       <c r="C1119" t="str">
         <v>441AR</v>
       </c>
       <c r="D1119" t="str">
-        <v>1.00</v>
+        <v>2.97</v>
       </c>
       <c r="E1119" t="str">
-        <v>70.000</v>
+        <v>1200.000</v>
       </c>
       <c r="F1119" t="str">
-        <v>0.000</v>
+        <v>1650.000</v>
       </c>
       <c r="G1119" t="str">
-        <v>COILS</v>
+        <v>BLANKS</v>
       </c>
       <c r="H1119" t="str">
         <v>2B</v>
       </c>
       <c r="I1119" t="str">
-        <v>1.600</v>
+        <v>1.800</v>
       </c>
     </row>
     <row r="1120">
       <c r="A1120" t="str">
-        <v>D0144751</v>
+        <v>C0897501</v>
       </c>
       <c r="B1120" t="str">
-        <v>1.790</v>
+        <v>323</v>
       </c>
       <c r="C1120" t="str">
         <v>441AR</v>
       </c>
       <c r="D1120" t="str">
-        <v>2.97</v>
+        <v>1.00</v>
       </c>
       <c r="E1120" t="str">
-        <v>1200.000</v>
+        <v>70.000</v>
       </c>
       <c r="F1120" t="str">
-        <v>1650.000</v>
+        <v>0.000</v>
       </c>
       <c r="G1120" t="str">
-        <v>BLANKS</v>
+        <v>COILS</v>
       </c>
       <c r="H1120" t="str">
         <v>2B</v>
       </c>
       <c r="I1120" t="str">
-        <v>1.800</v>
+        <v>1.600</v>
       </c>
     </row>
     <row r="1121">
@@ -33229,19 +33229,19 @@
     </row>
     <row r="1133">
       <c r="A1133" t="str">
-        <v>C0978487</v>
+        <v>D0142741</v>
       </c>
       <c r="B1133" t="str">
-        <v>615</v>
+        <v>428</v>
       </c>
       <c r="C1133" t="str">
         <v>441AR</v>
       </c>
       <c r="D1133" t="str">
-        <v>0.61</v>
+        <v>0.77</v>
       </c>
       <c r="E1133" t="str">
-        <v>170.000</v>
+        <v>215.000</v>
       </c>
       <c r="F1133" t="str">
         <v>0.000</v>
@@ -33253,24 +33253,24 @@
         <v>2B</v>
       </c>
       <c r="I1133" t="str">
-        <v>1.600</v>
+        <v>1.450</v>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" t="str">
-        <v>D0142741</v>
+        <v>C0978487</v>
       </c>
       <c r="B1134" t="str">
-        <v>428</v>
+        <v>615</v>
       </c>
       <c r="C1134" t="str">
         <v>441AR</v>
       </c>
       <c r="D1134" t="str">
-        <v>0.77</v>
+        <v>0.61</v>
       </c>
       <c r="E1134" t="str">
-        <v>215.000</v>
+        <v>170.000</v>
       </c>
       <c r="F1134" t="str">
         <v>0.000</v>
@@ -33282,7 +33282,7 @@
         <v>2B</v>
       </c>
       <c r="I1134" t="str">
-        <v>1.450</v>
+        <v>1.600</v>
       </c>
     </row>
     <row r="1135">
@@ -35868,19 +35868,19 @@
     </row>
     <row r="1224">
       <c r="A1224" t="str">
-        <v>C0976091</v>
+        <v>C0976083</v>
       </c>
       <c r="B1224" t="str">
-        <v>346</v>
+        <v>800</v>
       </c>
       <c r="C1224" t="str">
         <v>441AR</v>
       </c>
       <c r="D1224" t="str">
-        <v>0.51</v>
+        <v>0.82</v>
       </c>
       <c r="E1224" t="str">
-        <v>160.000</v>
+        <v>130.000</v>
       </c>
       <c r="F1224" t="str">
         <v>0.000</v>
@@ -35892,24 +35892,24 @@
         <v>2B</v>
       </c>
       <c r="I1224" t="str">
-        <v>1.650</v>
+        <v>1.600</v>
       </c>
     </row>
     <row r="1225">
       <c r="A1225" t="str">
-        <v>C0976083</v>
+        <v>C0976091</v>
       </c>
       <c r="B1225" t="str">
-        <v>800</v>
+        <v>346</v>
       </c>
       <c r="C1225" t="str">
         <v>441AR</v>
       </c>
       <c r="D1225" t="str">
-        <v>0.82</v>
+        <v>0.51</v>
       </c>
       <c r="E1225" t="str">
-        <v>130.000</v>
+        <v>160.000</v>
       </c>
       <c r="F1225" t="str">
         <v>0.000</v>
@@ -35921,7 +35921,7 @@
         <v>2B</v>
       </c>
       <c r="I1225" t="str">
-        <v>1.600</v>
+        <v>1.650</v>
       </c>
     </row>
     <row r="1226">
@@ -38420,19 +38420,19 @@
     </row>
     <row r="1312">
       <c r="A1312" t="str">
-        <v>D0146550</v>
+        <v>C0991763</v>
       </c>
       <c r="B1312" t="str">
-        <v>4.600</v>
+        <v>445</v>
       </c>
       <c r="C1312" t="str">
         <v>441AR</v>
       </c>
       <c r="D1312" t="str">
-        <v>1.72</v>
+        <v>1.00</v>
       </c>
       <c r="E1312" t="str">
-        <v>1270.000</v>
+        <v>130.000</v>
       </c>
       <c r="F1312" t="str">
         <v>0.000</v>
@@ -38444,24 +38444,24 @@
         <v>2B</v>
       </c>
       <c r="I1312" t="str">
-        <v>1.700</v>
+        <v>1.600</v>
       </c>
     </row>
     <row r="1313">
       <c r="A1313" t="str">
-        <v>C0991763</v>
+        <v>D0146550</v>
       </c>
       <c r="B1313" t="str">
-        <v>445</v>
+        <v>4.600</v>
       </c>
       <c r="C1313" t="str">
         <v>441AR</v>
       </c>
       <c r="D1313" t="str">
-        <v>1.00</v>
+        <v>1.72</v>
       </c>
       <c r="E1313" t="str">
-        <v>130.000</v>
+        <v>1270.000</v>
       </c>
       <c r="F1313" t="str">
         <v>0.000</v>
@@ -38473,7 +38473,7 @@
         <v>2B</v>
       </c>
       <c r="I1313" t="str">
-        <v>1.600</v>
+        <v>1.700</v>
       </c>
     </row>
     <row r="1314">
@@ -44191,10 +44191,10 @@
     </row>
     <row r="1511">
       <c r="A1511" t="str">
-        <v>C0992428</v>
+        <v>C0976197</v>
       </c>
       <c r="B1511" t="str">
-        <v>486</v>
+        <v>500</v>
       </c>
       <c r="C1511" t="str">
         <v>4513M</v>
@@ -44203,7 +44203,7 @@
         <v>0.81</v>
       </c>
       <c r="E1511" t="str">
-        <v>100.000</v>
+        <v>103.000</v>
       </c>
       <c r="F1511" t="str">
         <v>0.000</v>
@@ -44220,10 +44220,10 @@
     </row>
     <row r="1512">
       <c r="A1512" t="str">
-        <v>C0976197</v>
+        <v>C0992428</v>
       </c>
       <c r="B1512" t="str">
-        <v>500</v>
+        <v>486</v>
       </c>
       <c r="C1512" t="str">
         <v>4513M</v>
@@ -44232,7 +44232,7 @@
         <v>0.81</v>
       </c>
       <c r="E1512" t="str">
-        <v>103.000</v>
+        <v>100.000</v>
       </c>
       <c r="F1512" t="str">
         <v>0.000</v>
@@ -48831,16 +48831,16 @@
     </row>
     <row r="1671">
       <c r="A1671" t="str">
-        <v>D0131491</v>
+        <v>C0995467</v>
       </c>
       <c r="B1671" t="str">
-        <v>2.607</v>
+        <v>3.070</v>
       </c>
       <c r="C1671" t="str">
         <v>4828</v>
       </c>
       <c r="D1671" t="str">
-        <v>1.50</v>
+        <v>1.58</v>
       </c>
       <c r="E1671" t="str">
         <v>1272.000</v>
@@ -48855,21 +48855,21 @@
         <v>2B</v>
       </c>
       <c r="I1671" t="str">
-        <v>2.750</v>
+        <v>2.850</v>
       </c>
     </row>
     <row r="1672">
       <c r="A1672" t="str">
-        <v>C0995467</v>
+        <v>D0131491</v>
       </c>
       <c r="B1672" t="str">
-        <v>3.070</v>
+        <v>2.607</v>
       </c>
       <c r="C1672" t="str">
         <v>4828</v>
       </c>
       <c r="D1672" t="str">
-        <v>1.58</v>
+        <v>1.50</v>
       </c>
       <c r="E1672" t="str">
         <v>1272.000</v>
@@ -48884,7 +48884,7 @@
         <v>2B</v>
       </c>
       <c r="I1672" t="str">
-        <v>2.850</v>
+        <v>2.750</v>
       </c>
     </row>
     <row r="1673">
@@ -49498,19 +49498,19 @@
     </row>
     <row r="1694">
       <c r="A1694" t="str">
-        <v>C0990696</v>
+        <v>D0139116</v>
       </c>
       <c r="B1694" t="str">
-        <v>1.730</v>
+        <v>4.770</v>
       </c>
       <c r="C1694" t="str">
         <v>4828</v>
       </c>
       <c r="D1694" t="str">
-        <v>1.43</v>
+        <v>1.16</v>
       </c>
       <c r="E1694" t="str">
-        <v>108.000</v>
+        <v>1272.000</v>
       </c>
       <c r="F1694" t="str">
         <v>0.000</v>
@@ -49527,19 +49527,19 @@
     </row>
     <row r="1695">
       <c r="A1695" t="str">
-        <v>D0139116</v>
+        <v>C0990696</v>
       </c>
       <c r="B1695" t="str">
-        <v>4.770</v>
+        <v>1.730</v>
       </c>
       <c r="C1695" t="str">
         <v>4828</v>
       </c>
       <c r="D1695" t="str">
-        <v>1.16</v>
+        <v>1.43</v>
       </c>
       <c r="E1695" t="str">
-        <v>1272.000</v>
+        <v>108.000</v>
       </c>
       <c r="F1695" t="str">
         <v>0.000</v>
@@ -50426,19 +50426,19 @@
     </row>
     <row r="1726">
       <c r="A1726" t="str">
-        <v>D0145926</v>
+        <v>D0147340</v>
       </c>
       <c r="B1726" t="str">
-        <v>756</v>
+        <v>5.760</v>
       </c>
       <c r="C1726" t="str">
         <v>304DL</v>
       </c>
       <c r="D1726" t="str">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="E1726" t="str">
-        <v>240.000</v>
+        <v>1277.000</v>
       </c>
       <c r="F1726" t="str">
         <v>0.000</v>
@@ -50450,24 +50450,24 @@
         <v>2B</v>
       </c>
       <c r="I1726" t="str">
-        <v>2.250</v>
+        <v>2.350</v>
       </c>
     </row>
     <row r="1727">
       <c r="A1727" t="str">
-        <v>D0147340</v>
+        <v>D0145926</v>
       </c>
       <c r="B1727" t="str">
-        <v>5.760</v>
+        <v>756</v>
       </c>
       <c r="C1727" t="str">
         <v>304DL</v>
       </c>
       <c r="D1727" t="str">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="E1727" t="str">
-        <v>1277.000</v>
+        <v>240.000</v>
       </c>
       <c r="F1727" t="str">
         <v>0.000</v>
@@ -50479,7 +50479,7 @@
         <v>2B</v>
       </c>
       <c r="I1727" t="str">
-        <v>2.350</v>
+        <v>2.250</v>
       </c>
     </row>
     <row r="1728">
@@ -50629,60 +50629,60 @@
     </row>
     <row r="1733">
       <c r="A1733" t="str">
-        <v>D0147033</v>
+        <v>D0147123</v>
       </c>
       <c r="B1733" t="str">
-        <v>1.575</v>
+        <v>2.370</v>
       </c>
       <c r="C1733" t="str">
         <v>304DL</v>
       </c>
       <c r="D1733" t="str">
-        <v>4.94</v>
+        <v>1.40</v>
       </c>
       <c r="E1733" t="str">
-        <v>1500.000</v>
+        <v>1522.000</v>
       </c>
       <c r="F1733" t="str">
-        <v>3000.000</v>
+        <v>0.000</v>
       </c>
       <c r="G1733" t="str">
-        <v>BLANKS</v>
+        <v>COILS</v>
       </c>
       <c r="H1733" t="str">
         <v>2B</v>
       </c>
       <c r="I1733" t="str">
-        <v>2.750</v>
+        <v>2.250</v>
       </c>
     </row>
     <row r="1734">
       <c r="A1734" t="str">
-        <v>D0147123</v>
+        <v>D0147033</v>
       </c>
       <c r="B1734" t="str">
-        <v>2.370</v>
+        <v>1.575</v>
       </c>
       <c r="C1734" t="str">
         <v>304DL</v>
       </c>
       <c r="D1734" t="str">
-        <v>1.40</v>
+        <v>4.94</v>
       </c>
       <c r="E1734" t="str">
-        <v>1522.000</v>
+        <v>1500.000</v>
       </c>
       <c r="F1734" t="str">
-        <v>0.000</v>
+        <v>3000.000</v>
       </c>
       <c r="G1734" t="str">
-        <v>COILS</v>
+        <v>BLANKS</v>
       </c>
       <c r="H1734" t="str">
         <v>2B</v>
       </c>
       <c r="I1734" t="str">
-        <v>2.250</v>
+        <v>2.750</v>
       </c>
     </row>
     <row r="1735">
@@ -51354,22 +51354,22 @@
     </row>
     <row r="1758">
       <c r="A1758" t="str">
-        <v>D0146479</v>
+        <v>D0144568</v>
       </c>
       <c r="B1758" t="str">
-        <v>980</v>
+        <v>440</v>
       </c>
       <c r="C1758" t="str">
         <v>304DL</v>
       </c>
       <c r="D1758" t="str">
-        <v>3.97</v>
+        <v>1.50</v>
       </c>
       <c r="E1758" t="str">
-        <v>1250.000</v>
+        <v>1310.000</v>
       </c>
       <c r="F1758" t="str">
-        <v>2500.000</v>
+        <v>1900.000</v>
       </c>
       <c r="G1758" t="str">
         <v>BLANKS</v>
@@ -51378,27 +51378,27 @@
         <v>2B</v>
       </c>
       <c r="I1758" t="str">
-        <v>2.750</v>
+        <v>2.350</v>
       </c>
     </row>
     <row r="1759">
       <c r="A1759" t="str">
-        <v>D0144568</v>
+        <v>D0146479</v>
       </c>
       <c r="B1759" t="str">
-        <v>440</v>
+        <v>980</v>
       </c>
       <c r="C1759" t="str">
         <v>304DL</v>
       </c>
       <c r="D1759" t="str">
-        <v>1.50</v>
+        <v>3.97</v>
       </c>
       <c r="E1759" t="str">
-        <v>1310.000</v>
+        <v>1250.000</v>
       </c>
       <c r="F1759" t="str">
-        <v>1900.000</v>
+        <v>2500.000</v>
       </c>
       <c r="G1759" t="str">
         <v>BLANKS</v>
@@ -51407,7 +51407,7 @@
         <v>2B</v>
       </c>
       <c r="I1759" t="str">
-        <v>2.350</v>
+        <v>2.750</v>
       </c>
     </row>
     <row r="1760">
@@ -52369,60 +52369,60 @@
     </row>
     <row r="1793">
       <c r="A1793" t="str">
-        <v>D0146058</v>
+        <v>D0146310</v>
       </c>
       <c r="B1793" t="str">
-        <v>2.080</v>
+        <v>1.680</v>
       </c>
       <c r="C1793" t="str">
         <v>304DL</v>
       </c>
       <c r="D1793" t="str">
-        <v>1.00</v>
+        <v>2.97</v>
       </c>
       <c r="E1793" t="str">
-        <v>1522.000</v>
+        <v>1500.000</v>
       </c>
       <c r="F1793" t="str">
-        <v>0.000</v>
+        <v>3000.000</v>
       </c>
       <c r="G1793" t="str">
-        <v>COILS</v>
+        <v>BLANKS</v>
       </c>
       <c r="H1793" t="str">
         <v>2B</v>
       </c>
       <c r="I1793" t="str">
-        <v>2.250</v>
+        <v>2.750</v>
       </c>
     </row>
     <row r="1794">
       <c r="A1794" t="str">
-        <v>D0146310</v>
+        <v>D0146058</v>
       </c>
       <c r="B1794" t="str">
-        <v>1.680</v>
+        <v>2.080</v>
       </c>
       <c r="C1794" t="str">
         <v>304DL</v>
       </c>
       <c r="D1794" t="str">
-        <v>2.97</v>
+        <v>1.00</v>
       </c>
       <c r="E1794" t="str">
-        <v>1500.000</v>
+        <v>1522.000</v>
       </c>
       <c r="F1794" t="str">
-        <v>3000.000</v>
+        <v>0.000</v>
       </c>
       <c r="G1794" t="str">
-        <v>BLANKS</v>
+        <v>COILS</v>
       </c>
       <c r="H1794" t="str">
         <v>2B</v>
       </c>
       <c r="I1794" t="str">
-        <v>2.750</v>
+        <v>2.250</v>
       </c>
     </row>
     <row r="1795">
@@ -53239,22 +53239,22 @@
     </row>
     <row r="1823">
       <c r="A1823" t="str">
-        <v>D0142622</v>
+        <v>D0146483</v>
       </c>
       <c r="B1823" t="str">
-        <v>1.520</v>
+        <v>1.470</v>
       </c>
       <c r="C1823" t="str">
         <v>304DL</v>
       </c>
       <c r="D1823" t="str">
-        <v>0.81</v>
+        <v>3.96</v>
       </c>
       <c r="E1823" t="str">
         <v>1250.000</v>
       </c>
       <c r="F1823" t="str">
-        <v>2100.000</v>
+        <v>2500.000</v>
       </c>
       <c r="G1823" t="str">
         <v>BLANKS</v>
@@ -53263,27 +53263,27 @@
         <v>2B</v>
       </c>
       <c r="I1823" t="str">
-        <v>2.450</v>
+        <v>2.750</v>
       </c>
     </row>
     <row r="1824">
       <c r="A1824" t="str">
-        <v>D0146483</v>
+        <v>D0142622</v>
       </c>
       <c r="B1824" t="str">
-        <v>1.470</v>
+        <v>1.520</v>
       </c>
       <c r="C1824" t="str">
         <v>304DL</v>
       </c>
       <c r="D1824" t="str">
-        <v>3.96</v>
+        <v>0.81</v>
       </c>
       <c r="E1824" t="str">
         <v>1250.000</v>
       </c>
       <c r="F1824" t="str">
-        <v>2500.000</v>
+        <v>2100.000</v>
       </c>
       <c r="G1824" t="str">
         <v>BLANKS</v>
@@ -53292,7 +53292,7 @@
         <v>2B</v>
       </c>
       <c r="I1824" t="str">
-        <v>2.750</v>
+        <v>2.450</v>
       </c>
     </row>
     <row r="1825">
@@ -53442,22 +53442,22 @@
     </row>
     <row r="1830">
       <c r="A1830" t="str">
-        <v>D0147180</v>
+        <v>C0991166</v>
       </c>
       <c r="B1830" t="str">
-        <v>1.552</v>
+        <v>1.300</v>
       </c>
       <c r="C1830" t="str">
         <v>304DL</v>
       </c>
       <c r="D1830" t="str">
-        <v>1.00</v>
+        <v>1.20</v>
       </c>
       <c r="E1830" t="str">
-        <v>1000.000</v>
+        <v>1250.000</v>
       </c>
       <c r="F1830" t="str">
-        <v>2000.000</v>
+        <v>2500.000</v>
       </c>
       <c r="G1830" t="str">
         <v>BLANKS</v>
@@ -53471,22 +53471,22 @@
     </row>
     <row r="1831">
       <c r="A1831" t="str">
-        <v>C0991166</v>
+        <v>D0147180</v>
       </c>
       <c r="B1831" t="str">
-        <v>1.300</v>
+        <v>1.552</v>
       </c>
       <c r="C1831" t="str">
         <v>304DL</v>
       </c>
       <c r="D1831" t="str">
-        <v>1.20</v>
+        <v>1.00</v>
       </c>
       <c r="E1831" t="str">
-        <v>1250.000</v>
+        <v>1000.000</v>
       </c>
       <c r="F1831" t="str">
-        <v>2500.000</v>
+        <v>2000.000</v>
       </c>
       <c r="G1831" t="str">
         <v>BLANKS</v>
@@ -54254,16 +54254,16 @@
     </row>
     <row r="1858">
       <c r="A1858" t="str">
-        <v>D0147418</v>
+        <v>D0147114</v>
       </c>
       <c r="B1858" t="str">
-        <v>1.070</v>
+        <v>1.999</v>
       </c>
       <c r="C1858" t="str">
         <v>304DL</v>
       </c>
       <c r="D1858" t="str">
-        <v>1.00</v>
+        <v>2.96</v>
       </c>
       <c r="E1858" t="str">
         <v>1500.000</v>
@@ -54278,21 +54278,21 @@
         <v>2B</v>
       </c>
       <c r="I1858" t="str">
-        <v>2.650</v>
+        <v>2.750</v>
       </c>
     </row>
     <row r="1859">
       <c r="A1859" t="str">
-        <v>D0147114</v>
+        <v>D0147418</v>
       </c>
       <c r="B1859" t="str">
-        <v>1.999</v>
+        <v>1.070</v>
       </c>
       <c r="C1859" t="str">
         <v>304DL</v>
       </c>
       <c r="D1859" t="str">
-        <v>2.96</v>
+        <v>1.00</v>
       </c>
       <c r="E1859" t="str">
         <v>1500.000</v>
@@ -54307,7 +54307,7 @@
         <v>2B</v>
       </c>
       <c r="I1859" t="str">
-        <v>2.750</v>
+        <v>2.650</v>
       </c>
     </row>
     <row r="1860">
@@ -56226,60 +56226,60 @@
     </row>
     <row r="1926">
       <c r="A1926" t="str">
-        <v>D0143320</v>
+        <v>D0146660</v>
       </c>
       <c r="B1926" t="str">
-        <v>530</v>
+        <v>1.150</v>
       </c>
       <c r="C1926" t="str">
         <v>304DL</v>
       </c>
       <c r="D1926" t="str">
-        <v>0.97</v>
+        <v>1.00</v>
       </c>
       <c r="E1926" t="str">
-        <v>1500.000</v>
+        <v>1277.000</v>
       </c>
       <c r="F1926" t="str">
-        <v>3000.000</v>
+        <v>0.000</v>
       </c>
       <c r="G1926" t="str">
-        <v>BLANKS</v>
+        <v>COILS</v>
       </c>
       <c r="H1926" t="str">
         <v>2B</v>
       </c>
       <c r="I1926" t="str">
-        <v>2.650</v>
+        <v>2.250</v>
       </c>
     </row>
     <row r="1927">
       <c r="A1927" t="str">
-        <v>D0146660</v>
+        <v>D0143320</v>
       </c>
       <c r="B1927" t="str">
-        <v>1.150</v>
+        <v>530</v>
       </c>
       <c r="C1927" t="str">
         <v>304DL</v>
       </c>
       <c r="D1927" t="str">
-        <v>1.00</v>
+        <v>0.97</v>
       </c>
       <c r="E1927" t="str">
-        <v>1277.000</v>
+        <v>1500.000</v>
       </c>
       <c r="F1927" t="str">
-        <v>0.000</v>
+        <v>3000.000</v>
       </c>
       <c r="G1927" t="str">
-        <v>COILS</v>
+        <v>BLANKS</v>
       </c>
       <c r="H1927" t="str">
         <v>2B</v>
       </c>
       <c r="I1927" t="str">
-        <v>2.250</v>
+        <v>2.650</v>
       </c>
     </row>
     <row r="1928">
@@ -56487,118 +56487,118 @@
     </row>
     <row r="1935">
       <c r="A1935" t="str">
-        <v>D0147209</v>
+        <v>D0147197</v>
       </c>
       <c r="B1935" t="str">
-        <v>1.554</v>
+        <v>3.834</v>
       </c>
       <c r="C1935" t="str">
         <v>304DL</v>
       </c>
       <c r="D1935" t="str">
-        <v>0.81</v>
+        <v>0.61</v>
       </c>
       <c r="E1935" t="str">
-        <v>1500.000</v>
+        <v>450.000</v>
       </c>
       <c r="F1935" t="str">
-        <v>3000.000</v>
+        <v>0.000</v>
       </c>
       <c r="G1935" t="str">
-        <v>BLANKS</v>
+        <v>COILS</v>
       </c>
       <c r="H1935" t="str">
         <v>2B</v>
       </c>
       <c r="I1935" t="str">
-        <v>2.750</v>
+        <v>2.450</v>
       </c>
     </row>
     <row r="1936">
       <c r="A1936" t="str">
-        <v>D0147197</v>
+        <v>D0147209</v>
       </c>
       <c r="B1936" t="str">
-        <v>3.834</v>
+        <v>1.554</v>
       </c>
       <c r="C1936" t="str">
         <v>304DL</v>
       </c>
       <c r="D1936" t="str">
-        <v>0.61</v>
+        <v>0.81</v>
       </c>
       <c r="E1936" t="str">
-        <v>450.000</v>
+        <v>1500.000</v>
       </c>
       <c r="F1936" t="str">
-        <v>0.000</v>
+        <v>3000.000</v>
       </c>
       <c r="G1936" t="str">
-        <v>COILS</v>
+        <v>BLANKS</v>
       </c>
       <c r="H1936" t="str">
         <v>2B</v>
       </c>
       <c r="I1936" t="str">
-        <v>2.450</v>
+        <v>2.750</v>
       </c>
     </row>
     <row r="1937">
       <c r="A1937" t="str">
-        <v>D0144189</v>
+        <v>D0147136</v>
       </c>
       <c r="B1937" t="str">
-        <v>940</v>
+        <v>490</v>
       </c>
       <c r="C1937" t="str">
         <v>304DL</v>
       </c>
       <c r="D1937" t="str">
-        <v>3.97</v>
+        <v>1.00</v>
       </c>
       <c r="E1937" t="str">
-        <v>1500.000</v>
+        <v>1000.000</v>
       </c>
       <c r="F1937" t="str">
-        <v>0.000</v>
+        <v>2000.000</v>
       </c>
       <c r="G1937" t="str">
-        <v>COILS</v>
+        <v>BLANKS</v>
       </c>
       <c r="H1937" t="str">
         <v>2B</v>
       </c>
       <c r="I1937" t="str">
-        <v>2.250</v>
+        <v>2.650</v>
       </c>
     </row>
     <row r="1938">
       <c r="A1938" t="str">
-        <v>D0147136</v>
+        <v>D0144189</v>
       </c>
       <c r="B1938" t="str">
-        <v>490</v>
+        <v>940</v>
       </c>
       <c r="C1938" t="str">
         <v>304DL</v>
       </c>
       <c r="D1938" t="str">
-        <v>1.00</v>
+        <v>3.97</v>
       </c>
       <c r="E1938" t="str">
-        <v>1000.000</v>
+        <v>1500.000</v>
       </c>
       <c r="F1938" t="str">
-        <v>2000.000</v>
+        <v>0.000</v>
       </c>
       <c r="G1938" t="str">
-        <v>BLANKS</v>
+        <v>COILS</v>
       </c>
       <c r="H1938" t="str">
         <v>2B</v>
       </c>
       <c r="I1938" t="str">
-        <v>2.650</v>
+        <v>2.250</v>
       </c>
     </row>
     <row r="1939">
@@ -56806,19 +56806,19 @@
     </row>
     <row r="1946">
       <c r="A1946" t="str">
-        <v>D0147148</v>
+        <v>D0143261</v>
       </c>
       <c r="B1946" t="str">
-        <v>1.227</v>
+        <v>790</v>
       </c>
       <c r="C1946" t="str">
         <v>304DL</v>
       </c>
       <c r="D1946" t="str">
-        <v>4.97</v>
+        <v>0.78</v>
       </c>
       <c r="E1946" t="str">
-        <v>1250.000</v>
+        <v>1277.000</v>
       </c>
       <c r="F1946" t="str">
         <v>0.000</v>
@@ -56835,19 +56835,19 @@
     </row>
     <row r="1947">
       <c r="A1947" t="str">
-        <v>D0143261</v>
+        <v>D0147148</v>
       </c>
       <c r="B1947" t="str">
-        <v>790</v>
+        <v>1.227</v>
       </c>
       <c r="C1947" t="str">
         <v>304DL</v>
       </c>
       <c r="D1947" t="str">
-        <v>0.78</v>
+        <v>4.97</v>
       </c>
       <c r="E1947" t="str">
-        <v>1277.000</v>
+        <v>1250.000</v>
       </c>
       <c r="F1947" t="str">
         <v>0.000</v>
@@ -57966,10 +57966,10 @@
     </row>
     <row r="1986">
       <c r="A1986" t="str">
-        <v>D0146186</v>
+        <v>D0145912</v>
       </c>
       <c r="B1986" t="str">
-        <v>1.715</v>
+        <v>1.520</v>
       </c>
       <c r="C1986" t="str">
         <v>304DL</v>
@@ -57978,27 +57978,27 @@
         <v>3.97</v>
       </c>
       <c r="E1986" t="str">
-        <v>1277.000</v>
+        <v>1500.000</v>
       </c>
       <c r="F1986" t="str">
-        <v>2500.000</v>
+        <v>0.000</v>
       </c>
       <c r="G1986" t="str">
-        <v>BLANKS</v>
+        <v>COILS</v>
       </c>
       <c r="H1986" t="str">
         <v>2B</v>
       </c>
       <c r="I1986" t="str">
-        <v>2.450</v>
+        <v>2.250</v>
       </c>
     </row>
     <row r="1987">
       <c r="A1987" t="str">
-        <v>D0145912</v>
+        <v>D0146186</v>
       </c>
       <c r="B1987" t="str">
-        <v>1.520</v>
+        <v>1.715</v>
       </c>
       <c r="C1987" t="str">
         <v>304DL</v>
@@ -58007,19 +58007,19 @@
         <v>3.97</v>
       </c>
       <c r="E1987" t="str">
-        <v>1500.000</v>
+        <v>1277.000</v>
       </c>
       <c r="F1987" t="str">
-        <v>0.000</v>
+        <v>2500.000</v>
       </c>
       <c r="G1987" t="str">
-        <v>COILS</v>
+        <v>BLANKS</v>
       </c>
       <c r="H1987" t="str">
         <v>2B</v>
       </c>
       <c r="I1987" t="str">
-        <v>2.250</v>
+        <v>2.450</v>
       </c>
     </row>
     <row r="1988">
@@ -58053,22 +58053,22 @@
     </row>
     <row r="1989">
       <c r="A1989" t="str">
-        <v>D0146875</v>
+        <v>D0146055</v>
       </c>
       <c r="B1989" t="str">
-        <v>905</v>
+        <v>1.374</v>
       </c>
       <c r="C1989" t="str">
         <v>304DL</v>
       </c>
       <c r="D1989" t="str">
-        <v>1.97</v>
+        <v>0.78</v>
       </c>
       <c r="E1989" t="str">
-        <v>1000.000</v>
+        <v>1500.000</v>
       </c>
       <c r="F1989" t="str">
-        <v>2000.000</v>
+        <v>3000.000</v>
       </c>
       <c r="G1989" t="str">
         <v>BLANKS</v>
@@ -58082,22 +58082,22 @@
     </row>
     <row r="1990">
       <c r="A1990" t="str">
-        <v>D0146055</v>
+        <v>D0146875</v>
       </c>
       <c r="B1990" t="str">
-        <v>1.374</v>
+        <v>905</v>
       </c>
       <c r="C1990" t="str">
         <v>304DL</v>
       </c>
       <c r="D1990" t="str">
-        <v>0.78</v>
+        <v>1.97</v>
       </c>
       <c r="E1990" t="str">
-        <v>1500.000</v>
+        <v>1000.000</v>
       </c>
       <c r="F1990" t="str">
-        <v>3000.000</v>
+        <v>2000.000</v>
       </c>
       <c r="G1990" t="str">
         <v>BLANKS</v>
@@ -60518,16 +60518,16 @@
     </row>
     <row r="2074">
       <c r="A2074" t="str">
-        <v>D0146946</v>
+        <v>D0146564</v>
       </c>
       <c r="B2074" t="str">
-        <v>1.125</v>
+        <v>1.170</v>
       </c>
       <c r="C2074" t="str">
         <v>304DL</v>
       </c>
       <c r="D2074" t="str">
-        <v>3.95</v>
+        <v>2.05</v>
       </c>
       <c r="E2074" t="str">
         <v>1500.000</v>
@@ -60547,16 +60547,16 @@
     </row>
     <row r="2075">
       <c r="A2075" t="str">
-        <v>D0146564</v>
+        <v>D0146946</v>
       </c>
       <c r="B2075" t="str">
-        <v>1.170</v>
+        <v>1.125</v>
       </c>
       <c r="C2075" t="str">
         <v>304DL</v>
       </c>
       <c r="D2075" t="str">
-        <v>2.05</v>
+        <v>3.95</v>
       </c>
       <c r="E2075" t="str">
         <v>1500.000</v>
@@ -62374,60 +62374,60 @@
     </row>
     <row r="2138">
       <c r="A2138" t="str">
-        <v>D0142306</v>
+        <v>D0145712</v>
       </c>
       <c r="B2138" t="str">
-        <v>980</v>
+        <v>1.510</v>
       </c>
       <c r="C2138" t="str">
         <v>304DL</v>
       </c>
       <c r="D2138" t="str">
-        <v>0.81</v>
+        <v>1.52</v>
       </c>
       <c r="E2138" t="str">
-        <v>1500.000</v>
+        <v>1250.000</v>
       </c>
       <c r="F2138" t="str">
-        <v>0.000</v>
+        <v>2500.000</v>
       </c>
       <c r="G2138" t="str">
-        <v>COILS</v>
+        <v>BLANKS</v>
       </c>
       <c r="H2138" t="str">
         <v>2B</v>
       </c>
       <c r="I2138" t="str">
-        <v>2.250</v>
+        <v>2.750</v>
       </c>
     </row>
     <row r="2139">
       <c r="A2139" t="str">
-        <v>D0145712</v>
+        <v>D0142306</v>
       </c>
       <c r="B2139" t="str">
-        <v>1.510</v>
+        <v>980</v>
       </c>
       <c r="C2139" t="str">
         <v>304DL</v>
       </c>
       <c r="D2139" t="str">
-        <v>1.52</v>
+        <v>0.81</v>
       </c>
       <c r="E2139" t="str">
-        <v>1250.000</v>
+        <v>1500.000</v>
       </c>
       <c r="F2139" t="str">
-        <v>2500.000</v>
+        <v>0.000</v>
       </c>
       <c r="G2139" t="str">
-        <v>BLANKS</v>
+        <v>COILS</v>
       </c>
       <c r="H2139" t="str">
         <v>2B</v>
       </c>
       <c r="I2139" t="str">
-        <v>2.750</v>
+        <v>2.250</v>
       </c>
     </row>
     <row r="2140">
@@ -62606,60 +62606,60 @@
     </row>
     <row r="2146">
       <c r="A2146" t="str">
-        <v>D0146989</v>
+        <v>D0146180</v>
       </c>
       <c r="B2146" t="str">
-        <v>775</v>
+        <v>790</v>
       </c>
       <c r="C2146" t="str">
         <v>304DL</v>
       </c>
       <c r="D2146" t="str">
-        <v>3.96</v>
+        <v>1.97</v>
       </c>
       <c r="E2146" t="str">
-        <v>1250.000</v>
+        <v>1522.000</v>
       </c>
       <c r="F2146" t="str">
-        <v>2500.000</v>
+        <v>0.000</v>
       </c>
       <c r="G2146" t="str">
-        <v>BLANKS</v>
+        <v>COILS</v>
       </c>
       <c r="H2146" t="str">
         <v>2B</v>
       </c>
       <c r="I2146" t="str">
-        <v>2.750</v>
+        <v>2.250</v>
       </c>
     </row>
     <row r="2147">
       <c r="A2147" t="str">
-        <v>D0146180</v>
+        <v>D0146989</v>
       </c>
       <c r="B2147" t="str">
-        <v>790</v>
+        <v>775</v>
       </c>
       <c r="C2147" t="str">
         <v>304DL</v>
       </c>
       <c r="D2147" t="str">
-        <v>1.97</v>
+        <v>3.96</v>
       </c>
       <c r="E2147" t="str">
-        <v>1522.000</v>
+        <v>1250.000</v>
       </c>
       <c r="F2147" t="str">
-        <v>0.000</v>
+        <v>2500.000</v>
       </c>
       <c r="G2147" t="str">
-        <v>COILS</v>
+        <v>BLANKS</v>
       </c>
       <c r="H2147" t="str">
         <v>2B</v>
       </c>
       <c r="I2147" t="str">
-        <v>2.250</v>
+        <v>2.750</v>
       </c>
     </row>
     <row r="2148">
@@ -64143,60 +64143,60 @@
     </row>
     <row r="2199">
       <c r="A2199" t="str">
-        <v>D0145857</v>
+        <v>D0147302</v>
       </c>
       <c r="B2199" t="str">
-        <v>1.416</v>
+        <v>880</v>
       </c>
       <c r="C2199" t="str">
         <v>304DL</v>
       </c>
       <c r="D2199" t="str">
-        <v>3.97</v>
+        <v>1.97</v>
       </c>
       <c r="E2199" t="str">
-        <v>1500.000</v>
+        <v>1250.000</v>
       </c>
       <c r="F2199" t="str">
-        <v>0.000</v>
+        <v>2500.000</v>
       </c>
       <c r="G2199" t="str">
-        <v>COILS</v>
+        <v>BLANKS</v>
       </c>
       <c r="H2199" t="str">
         <v>2B</v>
       </c>
       <c r="I2199" t="str">
-        <v>2.250</v>
+        <v>2.750</v>
       </c>
     </row>
     <row r="2200">
       <c r="A2200" t="str">
-        <v>D0147302</v>
+        <v>D0145857</v>
       </c>
       <c r="B2200" t="str">
-        <v>880</v>
+        <v>1.416</v>
       </c>
       <c r="C2200" t="str">
         <v>304DL</v>
       </c>
       <c r="D2200" t="str">
-        <v>1.97</v>
+        <v>3.97</v>
       </c>
       <c r="E2200" t="str">
-        <v>1250.000</v>
+        <v>1500.000</v>
       </c>
       <c r="F2200" t="str">
-        <v>2500.000</v>
+        <v>0.000</v>
       </c>
       <c r="G2200" t="str">
-        <v>BLANKS</v>
+        <v>COILS</v>
       </c>
       <c r="H2200" t="str">
         <v>2B</v>
       </c>
       <c r="I2200" t="str">
-        <v>2.750</v>
+        <v>2.250</v>
       </c>
     </row>
     <row r="2201">
@@ -64433,22 +64433,22 @@
     </row>
     <row r="2209">
       <c r="A2209" t="str">
-        <v>D0145834</v>
+        <v>D0145084</v>
       </c>
       <c r="B2209" t="str">
-        <v>1.068</v>
+        <v>360</v>
       </c>
       <c r="C2209" t="str">
         <v>304DL</v>
       </c>
       <c r="D2209" t="str">
-        <v>1.98</v>
+        <v>1.02</v>
       </c>
       <c r="E2209" t="str">
-        <v>1250.000</v>
+        <v>1500.000</v>
       </c>
       <c r="F2209" t="str">
-        <v>2500.000</v>
+        <v>3000.000</v>
       </c>
       <c r="G2209" t="str">
         <v>BLANKS</v>
@@ -64462,22 +64462,22 @@
     </row>
     <row r="2210">
       <c r="A2210" t="str">
-        <v>D0145084</v>
+        <v>D0145834</v>
       </c>
       <c r="B2210" t="str">
-        <v>360</v>
+        <v>1.068</v>
       </c>
       <c r="C2210" t="str">
         <v>304DL</v>
       </c>
       <c r="D2210" t="str">
-        <v>1.02</v>
+        <v>1.98</v>
       </c>
       <c r="E2210" t="str">
-        <v>1500.000</v>
+        <v>1250.000</v>
       </c>
       <c r="F2210" t="str">
-        <v>3000.000</v>
+        <v>2500.000</v>
       </c>
       <c r="G2210" t="str">
         <v>BLANKS</v>
@@ -65100,22 +65100,22 @@
     </row>
     <row r="2232">
       <c r="A2232" t="str">
-        <v>D0146746</v>
+        <v>D0147426</v>
       </c>
       <c r="B2232" t="str">
-        <v>535</v>
+        <v>1.565</v>
       </c>
       <c r="C2232" t="str">
         <v>304DL</v>
       </c>
       <c r="D2232" t="str">
-        <v>1.97</v>
+        <v>4.94</v>
       </c>
       <c r="E2232" t="str">
-        <v>1250.000</v>
+        <v>1500.000</v>
       </c>
       <c r="F2232" t="str">
-        <v>2500.000</v>
+        <v>3000.000</v>
       </c>
       <c r="G2232" t="str">
         <v>BLANKS</v>
@@ -65124,27 +65124,27 @@
         <v>2B</v>
       </c>
       <c r="I2232" t="str">
-        <v>2.650</v>
+        <v>2.750</v>
       </c>
     </row>
     <row r="2233">
       <c r="A2233" t="str">
-        <v>D0147426</v>
+        <v>D0146746</v>
       </c>
       <c r="B2233" t="str">
-        <v>1.565</v>
+        <v>535</v>
       </c>
       <c r="C2233" t="str">
         <v>304DL</v>
       </c>
       <c r="D2233" t="str">
-        <v>4.94</v>
+        <v>1.97</v>
       </c>
       <c r="E2233" t="str">
-        <v>1500.000</v>
+        <v>1250.000</v>
       </c>
       <c r="F2233" t="str">
-        <v>3000.000</v>
+        <v>2500.000</v>
       </c>
       <c r="G2233" t="str">
         <v>BLANKS</v>
@@ -65153,7 +65153,7 @@
         <v>2B</v>
       </c>
       <c r="I2233" t="str">
-        <v>2.750</v>
+        <v>2.650</v>
       </c>
     </row>
     <row r="2234">
@@ -65332,16 +65332,16 @@
     </row>
     <row r="2240">
       <c r="A2240" t="str">
-        <v>D0147253</v>
+        <v>D0147200</v>
       </c>
       <c r="B2240" t="str">
-        <v>718</v>
+        <v>1.560</v>
       </c>
       <c r="C2240" t="str">
         <v>304DL</v>
       </c>
       <c r="D2240" t="str">
-        <v>2.96</v>
+        <v>0.81</v>
       </c>
       <c r="E2240" t="str">
         <v>1500.000</v>
@@ -65356,21 +65356,21 @@
         <v>2B</v>
       </c>
       <c r="I2240" t="str">
-        <v>2.650</v>
+        <v>2.750</v>
       </c>
     </row>
     <row r="2241">
       <c r="A2241" t="str">
-        <v>D0147200</v>
+        <v>D0147253</v>
       </c>
       <c r="B2241" t="str">
-        <v>1.560</v>
+        <v>718</v>
       </c>
       <c r="C2241" t="str">
         <v>304DL</v>
       </c>
       <c r="D2241" t="str">
-        <v>0.81</v>
+        <v>2.96</v>
       </c>
       <c r="E2241" t="str">
         <v>1500.000</v>
@@ -65385,65 +65385,65 @@
         <v>2B</v>
       </c>
       <c r="I2241" t="str">
-        <v>2.750</v>
+        <v>2.650</v>
       </c>
     </row>
     <row r="2242">
       <c r="A2242" t="str">
-        <v>D0146306</v>
+        <v>D0143789</v>
       </c>
       <c r="B2242" t="str">
-        <v>1.680</v>
+        <v>1.830</v>
       </c>
       <c r="C2242" t="str">
         <v>304DL</v>
       </c>
       <c r="D2242" t="str">
-        <v>2.97</v>
+        <v>4.94</v>
       </c>
       <c r="E2242" t="str">
-        <v>1500.000</v>
+        <v>1522.000</v>
       </c>
       <c r="F2242" t="str">
-        <v>3000.000</v>
+        <v>0.000</v>
       </c>
       <c r="G2242" t="str">
-        <v>BLANKS</v>
+        <v>COILS</v>
       </c>
       <c r="H2242" t="str">
         <v>2B</v>
       </c>
       <c r="I2242" t="str">
-        <v>2.750</v>
+        <v>2.250</v>
       </c>
     </row>
     <row r="2243">
       <c r="A2243" t="str">
-        <v>D0143789</v>
+        <v>D0146306</v>
       </c>
       <c r="B2243" t="str">
-        <v>1.830</v>
+        <v>1.680</v>
       </c>
       <c r="C2243" t="str">
         <v>304DL</v>
       </c>
       <c r="D2243" t="str">
-        <v>4.94</v>
+        <v>2.97</v>
       </c>
       <c r="E2243" t="str">
-        <v>1522.000</v>
+        <v>1500.000</v>
       </c>
       <c r="F2243" t="str">
-        <v>0.000</v>
+        <v>3000.000</v>
       </c>
       <c r="G2243" t="str">
-        <v>COILS</v>
+        <v>BLANKS</v>
       </c>
       <c r="H2243" t="str">
         <v>2B</v>
       </c>
       <c r="I2243" t="str">
-        <v>2.250</v>
+        <v>2.750</v>
       </c>
     </row>
     <row r="2244">
@@ -65738,22 +65738,22 @@
     </row>
     <row r="2254">
       <c r="A2254" t="str">
-        <v>D0146052</v>
+        <v>D0142308</v>
       </c>
       <c r="B2254" t="str">
-        <v>1.689</v>
+        <v>1.184</v>
       </c>
       <c r="C2254" t="str">
         <v>304DL</v>
       </c>
       <c r="D2254" t="str">
-        <v>1.98</v>
+        <v>0.78</v>
       </c>
       <c r="E2254" t="str">
         <v>1000.000</v>
       </c>
       <c r="F2254" t="str">
-        <v>2000.000</v>
+        <v>2496.000</v>
       </c>
       <c r="G2254" t="str">
         <v>BLANKS</v>
@@ -65762,27 +65762,27 @@
         <v>2B</v>
       </c>
       <c r="I2254" t="str">
-        <v>2.750</v>
+        <v>2.450</v>
       </c>
     </row>
     <row r="2255">
       <c r="A2255" t="str">
-        <v>D0142308</v>
+        <v>D0146052</v>
       </c>
       <c r="B2255" t="str">
-        <v>1.184</v>
+        <v>1.689</v>
       </c>
       <c r="C2255" t="str">
         <v>304DL</v>
       </c>
       <c r="D2255" t="str">
-        <v>0.78</v>
+        <v>1.98</v>
       </c>
       <c r="E2255" t="str">
         <v>1000.000</v>
       </c>
       <c r="F2255" t="str">
-        <v>2496.000</v>
+        <v>2000.000</v>
       </c>
       <c r="G2255" t="str">
         <v>BLANKS</v>
@@ -65791,7 +65791,7 @@
         <v>2B</v>
       </c>
       <c r="I2255" t="str">
-        <v>2.450</v>
+        <v>2.750</v>
       </c>
     </row>
     <row r="2256">
@@ -70436,22 +70436,22 @@
     </row>
     <row r="2416">
       <c r="A2416" t="str">
-        <v>D0144699</v>
+        <v>D0147353</v>
       </c>
       <c r="B2416" t="str">
-        <v>1.940</v>
+        <v>570</v>
       </c>
       <c r="C2416" t="str">
         <v>316L</v>
       </c>
       <c r="D2416" t="str">
-        <v>4.97</v>
+        <v>3.96</v>
       </c>
       <c r="E2416" t="str">
-        <v>1500.000</v>
+        <v>1000.000</v>
       </c>
       <c r="F2416" t="str">
-        <v>3000.000</v>
+        <v>2000.000</v>
       </c>
       <c r="G2416" t="str">
         <v>BLANKS</v>
@@ -70460,27 +70460,27 @@
         <v>2B</v>
       </c>
       <c r="I2416" t="str">
-        <v>4.000</v>
+        <v>3.900</v>
       </c>
     </row>
     <row r="2417">
       <c r="A2417" t="str">
-        <v>D0147353</v>
+        <v>D0144699</v>
       </c>
       <c r="B2417" t="str">
-        <v>570</v>
+        <v>1.940</v>
       </c>
       <c r="C2417" t="str">
         <v>316L</v>
       </c>
       <c r="D2417" t="str">
-        <v>3.96</v>
+        <v>4.97</v>
       </c>
       <c r="E2417" t="str">
-        <v>1000.000</v>
+        <v>1500.000</v>
       </c>
       <c r="F2417" t="str">
-        <v>2000.000</v>
+        <v>3000.000</v>
       </c>
       <c r="G2417" t="str">
         <v>BLANKS</v>
@@ -70489,7 +70489,7 @@
         <v>2B</v>
       </c>
       <c r="I2417" t="str">
-        <v>3.900</v>
+        <v>4.000</v>
       </c>
     </row>
     <row r="2418">
@@ -71306,22 +71306,22 @@
     </row>
     <row r="2446">
       <c r="A2446" t="str">
-        <v>C0990727</v>
+        <v>D0146292</v>
       </c>
       <c r="B2446" t="str">
-        <v>1.500</v>
+        <v>1.342</v>
       </c>
       <c r="C2446" t="str">
         <v>316L</v>
       </c>
       <c r="D2446" t="str">
-        <v>5.08</v>
+        <v>2.96</v>
       </c>
       <c r="E2446" t="str">
-        <v>1250.000</v>
+        <v>1500.000</v>
       </c>
       <c r="F2446" t="str">
-        <v>2500.000</v>
+        <v>3000.000</v>
       </c>
       <c r="G2446" t="str">
         <v>BLANKS</v>
@@ -71330,27 +71330,27 @@
         <v>2B</v>
       </c>
       <c r="I2446" t="str">
-        <v>4.050</v>
+        <v>4.000</v>
       </c>
     </row>
     <row r="2447">
       <c r="A2447" t="str">
-        <v>D0146292</v>
+        <v>C0990727</v>
       </c>
       <c r="B2447" t="str">
-        <v>1.342</v>
+        <v>1.500</v>
       </c>
       <c r="C2447" t="str">
         <v>316L</v>
       </c>
       <c r="D2447" t="str">
-        <v>2.96</v>
+        <v>5.08</v>
       </c>
       <c r="E2447" t="str">
-        <v>1500.000</v>
+        <v>1250.000</v>
       </c>
       <c r="F2447" t="str">
-        <v>3000.000</v>
+        <v>2500.000</v>
       </c>
       <c r="G2447" t="str">
         <v>BLANKS</v>
@@ -71359,7 +71359,7 @@
         <v>2B</v>
       </c>
       <c r="I2447" t="str">
-        <v>4.000</v>
+        <v>4.050</v>
       </c>
     </row>
     <row r="2448">
@@ -72669,16 +72669,16 @@
     </row>
     <row r="2493">
       <c r="A2493" t="str">
-        <v>D0145047</v>
+        <v>D0146819</v>
       </c>
       <c r="B2493" t="str">
-        <v>2.800</v>
+        <v>1.530</v>
       </c>
       <c r="C2493" t="str">
         <v>316L</v>
       </c>
       <c r="D2493" t="str">
-        <v>1.98</v>
+        <v>0.61</v>
       </c>
       <c r="E2493" t="str">
         <v>1522.000</v>
@@ -72693,21 +72693,21 @@
         <v>2B</v>
       </c>
       <c r="I2493" t="str">
-        <v>3.500</v>
+        <v>3.600</v>
       </c>
     </row>
     <row r="2494">
       <c r="A2494" t="str">
-        <v>D0146819</v>
+        <v>D0145047</v>
       </c>
       <c r="B2494" t="str">
-        <v>1.530</v>
+        <v>2.800</v>
       </c>
       <c r="C2494" t="str">
         <v>316L</v>
       </c>
       <c r="D2494" t="str">
-        <v>0.61</v>
+        <v>1.98</v>
       </c>
       <c r="E2494" t="str">
         <v>1522.000</v>
@@ -72722,7 +72722,7 @@
         <v>2B</v>
       </c>
       <c r="I2494" t="str">
-        <v>3.600</v>
+        <v>3.500</v>
       </c>
     </row>
     <row r="2495">
@@ -73597,60 +73597,60 @@
     </row>
     <row r="2525">
       <c r="A2525" t="str">
-        <v>D0146633</v>
+        <v>D0146342</v>
       </c>
       <c r="B2525" t="str">
-        <v>1.330</v>
+        <v>2.180</v>
       </c>
       <c r="C2525" t="str">
         <v>316L</v>
       </c>
       <c r="D2525" t="str">
-        <v>2.05</v>
+        <v>0.61</v>
       </c>
       <c r="E2525" t="str">
-        <v>1000.000</v>
+        <v>130.000</v>
       </c>
       <c r="F2525" t="str">
-        <v>2000.000</v>
+        <v>0.000</v>
       </c>
       <c r="G2525" t="str">
-        <v>BLANKS</v>
+        <v>COILS</v>
       </c>
       <c r="H2525" t="str">
         <v>2B</v>
       </c>
       <c r="I2525" t="str">
-        <v>4.000</v>
+        <v>3.600</v>
       </c>
     </row>
     <row r="2526">
       <c r="A2526" t="str">
-        <v>D0146342</v>
+        <v>D0146633</v>
       </c>
       <c r="B2526" t="str">
-        <v>2.180</v>
+        <v>1.330</v>
       </c>
       <c r="C2526" t="str">
         <v>316L</v>
       </c>
       <c r="D2526" t="str">
-        <v>0.61</v>
+        <v>2.05</v>
       </c>
       <c r="E2526" t="str">
-        <v>130.000</v>
+        <v>1000.000</v>
       </c>
       <c r="F2526" t="str">
-        <v>0.000</v>
+        <v>2000.000</v>
       </c>
       <c r="G2526" t="str">
-        <v>COILS</v>
+        <v>BLANKS</v>
       </c>
       <c r="H2526" t="str">
         <v>2B</v>
       </c>
       <c r="I2526" t="str">
-        <v>3.600</v>
+        <v>4.000</v>
       </c>
     </row>
     <row r="2527">
@@ -74032,19 +74032,19 @@
     </row>
     <row r="2540">
       <c r="A2540" t="str">
-        <v>C0990894</v>
+        <v>D0146903</v>
       </c>
       <c r="B2540" t="str">
-        <v>1.534</v>
+        <v>3.990</v>
       </c>
       <c r="C2540" t="str">
         <v>316LSM</v>
       </c>
       <c r="D2540" t="str">
-        <v>1.17</v>
+        <v>1.91</v>
       </c>
       <c r="E2540" t="str">
-        <v>105.000</v>
+        <v>1272.000</v>
       </c>
       <c r="F2540" t="str">
         <v>0.000</v>
@@ -74056,24 +74056,24 @@
         <v>2B</v>
       </c>
       <c r="I2540" t="str">
-        <v>3.650</v>
+        <v>3.700</v>
       </c>
     </row>
     <row r="2541">
       <c r="A2541" t="str">
-        <v>D0146903</v>
+        <v>C0990894</v>
       </c>
       <c r="B2541" t="str">
-        <v>3.990</v>
+        <v>1.534</v>
       </c>
       <c r="C2541" t="str">
         <v>316LSM</v>
       </c>
       <c r="D2541" t="str">
-        <v>1.91</v>
+        <v>1.17</v>
       </c>
       <c r="E2541" t="str">
-        <v>1272.000</v>
+        <v>105.000</v>
       </c>
       <c r="F2541" t="str">
         <v>0.000</v>
@@ -74085,7 +74085,7 @@
         <v>2B</v>
       </c>
       <c r="I2541" t="str">
-        <v>3.700</v>
+        <v>3.650</v>
       </c>
     </row>
     <row r="2542">
@@ -77483,19 +77483,19 @@
     </row>
     <row r="2659">
       <c r="A2659" t="str">
-        <v>C0949630</v>
+        <v>C0983606</v>
       </c>
       <c r="B2659" t="str">
-        <v>1.350</v>
+        <v>2.842</v>
       </c>
       <c r="C2659" t="str">
         <v>321</v>
       </c>
       <c r="D2659" t="str">
-        <v>2.18</v>
+        <v>2.58</v>
       </c>
       <c r="E2659" t="str">
-        <v>160.000</v>
+        <v>220.000</v>
       </c>
       <c r="F2659" t="str">
         <v>0.000</v>
@@ -77512,19 +77512,19 @@
     </row>
     <row r="2660">
       <c r="A2660" t="str">
-        <v>C0983606</v>
+        <v>C0949630</v>
       </c>
       <c r="B2660" t="str">
-        <v>2.842</v>
+        <v>1.350</v>
       </c>
       <c r="C2660" t="str">
         <v>321</v>
       </c>
       <c r="D2660" t="str">
-        <v>2.58</v>
+        <v>2.18</v>
       </c>
       <c r="E2660" t="str">
-        <v>220.000</v>
+        <v>160.000</v>
       </c>
       <c r="F2660" t="str">
         <v>0.000</v>
@@ -77715,19 +77715,19 @@
     </row>
     <row r="2667">
       <c r="A2667" t="str">
-        <v>C0928551</v>
+        <v>C0967732</v>
       </c>
       <c r="B2667" t="str">
-        <v>676</v>
+        <v>3.732</v>
       </c>
       <c r="C2667" t="str">
         <v>321</v>
       </c>
       <c r="D2667" t="str">
-        <v>1.51</v>
+        <v>2.58</v>
       </c>
       <c r="E2667" t="str">
-        <v>90.000</v>
+        <v>235.000</v>
       </c>
       <c r="F2667" t="str">
         <v>0.000</v>
@@ -77739,24 +77739,24 @@
         <v>2B</v>
       </c>
       <c r="I2667" t="str">
-        <v>2.450</v>
+        <v>2.650</v>
       </c>
     </row>
     <row r="2668">
       <c r="A2668" t="str">
-        <v>C0967732</v>
+        <v>C0928551</v>
       </c>
       <c r="B2668" t="str">
-        <v>3.732</v>
+        <v>676</v>
       </c>
       <c r="C2668" t="str">
         <v>321</v>
       </c>
       <c r="D2668" t="str">
-        <v>2.58</v>
+        <v>1.51</v>
       </c>
       <c r="E2668" t="str">
-        <v>235.000</v>
+        <v>90.000</v>
       </c>
       <c r="F2668" t="str">
         <v>0.000</v>
@@ -77768,7 +77768,7 @@
         <v>2B</v>
       </c>
       <c r="I2668" t="str">
-        <v>2.650</v>
+        <v>2.450</v>
       </c>
     </row>
     <row r="2669">
@@ -78817,77 +78817,77 @@
     </row>
     <row r="2705">
       <c r="A2705" t="str">
-        <v>D0146199</v>
+        <v>C0967720</v>
       </c>
       <c r="B2705" t="str">
-        <v>565</v>
+        <v>934</v>
       </c>
       <c r="C2705" t="str">
         <v>321</v>
       </c>
       <c r="D2705" t="str">
-        <v>2.08</v>
+        <v>1.19</v>
       </c>
       <c r="E2705" t="str">
-        <v>1250.000</v>
+        <v>80.000</v>
       </c>
       <c r="F2705" t="str">
-        <v>2500.000</v>
+        <v>0.000</v>
       </c>
       <c r="G2705" t="str">
-        <v>BLANKS</v>
+        <v>COILS</v>
       </c>
       <c r="H2705" t="str">
         <v>2B</v>
       </c>
       <c r="I2705" t="str">
-        <v>2.750</v>
+        <v>2.450</v>
       </c>
     </row>
     <row r="2706">
       <c r="A2706" t="str">
-        <v>C0898763</v>
+        <v>D0146199</v>
       </c>
       <c r="B2706" t="str">
-        <v>6.830</v>
+        <v>565</v>
       </c>
       <c r="C2706" t="str">
         <v>321</v>
       </c>
       <c r="D2706" t="str">
-        <v>2.58</v>
+        <v>2.08</v>
       </c>
       <c r="E2706" t="str">
-        <v>430.000</v>
+        <v>1250.000</v>
       </c>
       <c r="F2706" t="str">
-        <v>0.000</v>
+        <v>2500.000</v>
       </c>
       <c r="G2706" t="str">
-        <v>COILS</v>
+        <v>BLANKS</v>
       </c>
       <c r="H2706" t="str">
         <v>2B</v>
       </c>
       <c r="I2706" t="str">
-        <v>2.650</v>
+        <v>2.750</v>
       </c>
     </row>
     <row r="2707">
       <c r="A2707" t="str">
-        <v>C0967720</v>
+        <v>C0898763</v>
       </c>
       <c r="B2707" t="str">
-        <v>934</v>
+        <v>6.830</v>
       </c>
       <c r="C2707" t="str">
         <v>321</v>
       </c>
       <c r="D2707" t="str">
-        <v>1.19</v>
+        <v>2.58</v>
       </c>
       <c r="E2707" t="str">
-        <v>80.000</v>
+        <v>430.000</v>
       </c>
       <c r="F2707" t="str">
         <v>0.000</v>
@@ -78899,7 +78899,7 @@
         <v>2B</v>
       </c>
       <c r="I2707" t="str">
-        <v>2.450</v>
+        <v>2.650</v>
       </c>
     </row>
     <row r="2708">

--- a/arvedi_data.xlsx
+++ b/arvedi_data.xlsx
@@ -7545,28 +7545,28 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>C1027405</v>
+        <v>D0145804</v>
       </c>
       <c r="B189" t="str">
-        <v>1.094</v>
+        <v>618</v>
       </c>
       <c r="C189" t="str">
         <v>304DL</v>
       </c>
       <c r="D189" t="str">
-        <v>1.00</v>
+        <v>0.39</v>
       </c>
       <c r="E189" t="str">
-        <v>1000.000</v>
+        <v>79.000</v>
       </c>
       <c r="F189" t="str">
-        <v>2000.000</v>
+        <v>0.000</v>
       </c>
       <c r="G189" t="str">
-        <v>BLANKS</v>
+        <v>COILS</v>
       </c>
       <c r="H189" t="str">
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="I189" t="str">
         <v>2</v>
@@ -7578,33 +7578,33 @@
         <v>NO</v>
       </c>
       <c r="L189" t="str">
-        <v>2.650</v>
+        <v>2.250</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>D0145804</v>
+        <v>C1027405</v>
       </c>
       <c r="B190" t="str">
-        <v>618</v>
+        <v>1.094</v>
       </c>
       <c r="C190" t="str">
         <v>304DL</v>
       </c>
       <c r="D190" t="str">
-        <v>0.39</v>
+        <v>1.00</v>
       </c>
       <c r="E190" t="str">
-        <v>79.000</v>
+        <v>1000.000</v>
       </c>
       <c r="F190" t="str">
-        <v>0.000</v>
+        <v>2000.000</v>
       </c>
       <c r="G190" t="str">
-        <v>COILS</v>
+        <v>BLANKS</v>
       </c>
       <c r="H190" t="str">
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="I190" t="str">
         <v>2</v>
@@ -7616,7 +7616,7 @@
         <v>NO</v>
       </c>
       <c r="L190" t="str">
-        <v>2.250</v>
+        <v>2.650</v>
       </c>
     </row>
     <row r="191">
@@ -9103,19 +9103,19 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>C1003553</v>
+        <v>D0148542</v>
       </c>
       <c r="B230" t="str">
-        <v>776</v>
+        <v>828</v>
       </c>
       <c r="C230" t="str">
         <v>304MSA</v>
       </c>
       <c r="D230" t="str">
-        <v>0.91</v>
+        <v>0.42</v>
       </c>
       <c r="E230" t="str">
-        <v>200.000</v>
+        <v>536.500</v>
       </c>
       <c r="F230" t="str">
         <v>0.000</v>
@@ -9127,7 +9127,7 @@
         <v>R</v>
       </c>
       <c r="I230" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J230" t="str">
         <v>BA</v>
@@ -9141,19 +9141,19 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>D0148542</v>
+        <v>C1003553</v>
       </c>
       <c r="B231" t="str">
-        <v>828</v>
+        <v>776</v>
       </c>
       <c r="C231" t="str">
         <v>304MSA</v>
       </c>
       <c r="D231" t="str">
-        <v>0.42</v>
+        <v>0.91</v>
       </c>
       <c r="E231" t="str">
-        <v>536.500</v>
+        <v>200.000</v>
       </c>
       <c r="F231" t="str">
         <v>0.000</v>
@@ -9165,7 +9165,7 @@
         <v>R</v>
       </c>
       <c r="I231" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J231" t="str">
         <v>BA</v>
@@ -9635,28 +9635,28 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>D0148365</v>
+        <v>D0148217</v>
       </c>
       <c r="B244" t="str">
-        <v>1.443</v>
+        <v>668</v>
       </c>
       <c r="C244" t="str">
         <v>304MSA</v>
       </c>
       <c r="D244" t="str">
-        <v>0.40</v>
+        <v>0.42</v>
       </c>
       <c r="E244" t="str">
-        <v>1522.000</v>
+        <v>718.000</v>
       </c>
       <c r="F244" t="str">
-        <v>0.000</v>
+        <v>701.000</v>
       </c>
       <c r="G244" t="str">
-        <v>COILS</v>
+        <v>BLANKS</v>
       </c>
       <c r="H244" t="str">
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="I244" t="str">
         <v>2</v>
@@ -9668,33 +9668,33 @@
         <v>NO</v>
       </c>
       <c r="L244" t="str">
-        <v>2.350</v>
+        <v>2.450</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>D0148217</v>
+        <v>D0148365</v>
       </c>
       <c r="B245" t="str">
-        <v>668</v>
+        <v>1.443</v>
       </c>
       <c r="C245" t="str">
         <v>304MSA</v>
       </c>
       <c r="D245" t="str">
-        <v>0.42</v>
+        <v>0.40</v>
       </c>
       <c r="E245" t="str">
-        <v>718.000</v>
+        <v>1522.000</v>
       </c>
       <c r="F245" t="str">
-        <v>701.000</v>
+        <v>0.000</v>
       </c>
       <c r="G245" t="str">
-        <v>BLANKS</v>
+        <v>COILS</v>
       </c>
       <c r="H245" t="str">
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="I245" t="str">
         <v>2</v>
@@ -9706,7 +9706,7 @@
         <v>NO</v>
       </c>
       <c r="L245" t="str">
-        <v>2.450</v>
+        <v>2.350</v>
       </c>
     </row>
     <row r="246">
@@ -10699,10 +10699,10 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>D0149419</v>
+        <v>D0149391</v>
       </c>
       <c r="B272" t="str">
-        <v>1.961</v>
+        <v>1.773</v>
       </c>
       <c r="C272" t="str">
         <v>304PS</v>
@@ -10711,7 +10711,7 @@
         <v>0.62</v>
       </c>
       <c r="E272" t="str">
-        <v>380.000</v>
+        <v>1522.000</v>
       </c>
       <c r="F272" t="str">
         <v>0.000</v>
@@ -10720,7 +10720,7 @@
         <v>COILS</v>
       </c>
       <c r="H272" t="str">
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="I272" t="str">
         <v>2</v>
@@ -10737,10 +10737,10 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>D0149391</v>
+        <v>D0149419</v>
       </c>
       <c r="B273" t="str">
-        <v>1.773</v>
+        <v>1.961</v>
       </c>
       <c r="C273" t="str">
         <v>304PS</v>
@@ -10749,7 +10749,7 @@
         <v>0.62</v>
       </c>
       <c r="E273" t="str">
-        <v>1522.000</v>
+        <v>380.000</v>
       </c>
       <c r="F273" t="str">
         <v>0.000</v>
@@ -10758,7 +10758,7 @@
         <v>COILS</v>
       </c>
       <c r="H273" t="str">
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="I273" t="str">
         <v>2</v>
@@ -15373,19 +15373,19 @@
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>C1018283</v>
+        <v>C1027489</v>
       </c>
       <c r="B395" t="str">
-        <v>555</v>
+        <v>888</v>
       </c>
       <c r="C395" t="str">
         <v>409LI</v>
       </c>
       <c r="D395" t="str">
-        <v>0.81</v>
+        <v>1.00</v>
       </c>
       <c r="E395" t="str">
-        <v>178.000</v>
+        <v>190.000</v>
       </c>
       <c r="F395" t="str">
         <v>0.000</v>
@@ -15411,19 +15411,19 @@
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>C1027489</v>
+        <v>C1018283</v>
       </c>
       <c r="B396" t="str">
-        <v>888</v>
+        <v>555</v>
       </c>
       <c r="C396" t="str">
         <v>409LI</v>
       </c>
       <c r="D396" t="str">
-        <v>1.00</v>
+        <v>0.81</v>
       </c>
       <c r="E396" t="str">
-        <v>190.000</v>
+        <v>178.000</v>
       </c>
       <c r="F396" t="str">
         <v>0.000</v>
@@ -18375,19 +18375,19 @@
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>C0984684</v>
+        <v>C0995195</v>
       </c>
       <c r="B474" t="str">
-        <v>947</v>
+        <v>559</v>
       </c>
       <c r="C474" t="str">
         <v>439M</v>
       </c>
       <c r="D474" t="str">
-        <v>0.61</v>
+        <v>0.81</v>
       </c>
       <c r="E474" t="str">
-        <v>280.000</v>
+        <v>220.000</v>
       </c>
       <c r="F474" t="str">
         <v>0.000</v>
@@ -18413,19 +18413,19 @@
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>C0995195</v>
+        <v>C0984684</v>
       </c>
       <c r="B475" t="str">
-        <v>559</v>
+        <v>947</v>
       </c>
       <c r="C475" t="str">
         <v>439M</v>
       </c>
       <c r="D475" t="str">
-        <v>0.81</v>
+        <v>0.61</v>
       </c>
       <c r="E475" t="str">
-        <v>220.000</v>
+        <v>280.000</v>
       </c>
       <c r="F475" t="str">
         <v>0.000</v>
@@ -19515,10 +19515,10 @@
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>C1014531</v>
+        <v>C1018926</v>
       </c>
       <c r="B504" t="str">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="C504" t="str">
         <v>439M</v>
@@ -19553,10 +19553,10 @@
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>C1018926</v>
+        <v>C1014531</v>
       </c>
       <c r="B505" t="str">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="C505" t="str">
         <v>439M</v>
@@ -21149,19 +21149,19 @@
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>C0991714</v>
+        <v>C1004071</v>
       </c>
       <c r="B547" t="str">
-        <v>1.070</v>
+        <v>2.113</v>
       </c>
       <c r="C547" t="str">
         <v>441AR</v>
       </c>
       <c r="D547" t="str">
-        <v>0.61</v>
+        <v>2.97</v>
       </c>
       <c r="E547" t="str">
-        <v>300.000</v>
+        <v>154.000</v>
       </c>
       <c r="F547" t="str">
         <v>0.000</v>
@@ -21187,19 +21187,19 @@
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>C1004071</v>
+        <v>C0991714</v>
       </c>
       <c r="B548" t="str">
-        <v>2.113</v>
+        <v>1.070</v>
       </c>
       <c r="C548" t="str">
         <v>441AR</v>
       </c>
       <c r="D548" t="str">
-        <v>2.97</v>
+        <v>0.61</v>
       </c>
       <c r="E548" t="str">
-        <v>154.000</v>
+        <v>300.000</v>
       </c>
       <c r="F548" t="str">
         <v>0.000</v>
@@ -21681,16 +21681,16 @@
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>D0149099</v>
+        <v>D0148587</v>
       </c>
       <c r="B561" t="str">
-        <v>658</v>
+        <v>441</v>
       </c>
       <c r="C561" t="str">
         <v>441AR</v>
       </c>
       <c r="D561" t="str">
-        <v>0.61</v>
+        <v>2.97</v>
       </c>
       <c r="E561" t="str">
         <v>200.000</v>
@@ -21719,16 +21719,16 @@
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>D0148587</v>
+        <v>D0149099</v>
       </c>
       <c r="B562" t="str">
-        <v>441</v>
+        <v>658</v>
       </c>
       <c r="C562" t="str">
         <v>441AR</v>
       </c>
       <c r="D562" t="str">
-        <v>2.97</v>
+        <v>0.61</v>
       </c>
       <c r="E562" t="str">
         <v>200.000</v>
@@ -23087,19 +23087,19 @@
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>D0149740</v>
+        <v>C0982452</v>
       </c>
       <c r="B598" t="str">
-        <v>1.369</v>
+        <v>318</v>
       </c>
       <c r="C598" t="str">
         <v>441AR</v>
       </c>
       <c r="D598" t="str">
-        <v>1.00</v>
+        <v>1.98</v>
       </c>
       <c r="E598" t="str">
-        <v>1270.000</v>
+        <v>78.500</v>
       </c>
       <c r="F598" t="str">
         <v>0.000</v>
@@ -23108,10 +23108,10 @@
         <v>COILS</v>
       </c>
       <c r="H598" t="str">
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="I598" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J598" t="str">
         <v>2B</v>
@@ -23125,19 +23125,19 @@
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>C0982452</v>
+        <v>D0149740</v>
       </c>
       <c r="B599" t="str">
-        <v>318</v>
+        <v>1.369</v>
       </c>
       <c r="C599" t="str">
         <v>441AR</v>
       </c>
       <c r="D599" t="str">
-        <v>1.98</v>
+        <v>1.00</v>
       </c>
       <c r="E599" t="str">
-        <v>78.500</v>
+        <v>1270.000</v>
       </c>
       <c r="F599" t="str">
         <v>0.000</v>
@@ -23146,10 +23146,10 @@
         <v>COILS</v>
       </c>
       <c r="H599" t="str">
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="I599" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J599" t="str">
         <v>2B</v>
@@ -23163,10 +23163,10 @@
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>D0146437</v>
+        <v>D0148417</v>
       </c>
       <c r="B600" t="str">
-        <v>1.071</v>
+        <v>1.226</v>
       </c>
       <c r="C600" t="str">
         <v>441AR</v>
@@ -23196,15 +23196,15 @@
         <v>NO</v>
       </c>
       <c r="L600" t="str">
-        <v>1.570</v>
+        <v>1.600</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>D0148417</v>
+        <v>D0146437</v>
       </c>
       <c r="B601" t="str">
-        <v>1.226</v>
+        <v>1.071</v>
       </c>
       <c r="C601" t="str">
         <v>441AR</v>
@@ -23234,7 +23234,7 @@
         <v>NO</v>
       </c>
       <c r="L601" t="str">
-        <v>1.600</v>
+        <v>1.570</v>
       </c>
     </row>
     <row r="602">
@@ -24265,19 +24265,19 @@
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>D0143676</v>
+        <v>D0145703</v>
       </c>
       <c r="B629" t="str">
-        <v>700</v>
+        <v>810</v>
       </c>
       <c r="C629" t="str">
         <v>441AR</v>
       </c>
       <c r="D629" t="str">
-        <v>0.61</v>
+        <v>0.71</v>
       </c>
       <c r="E629" t="str">
-        <v>1270.000</v>
+        <v>380.000</v>
       </c>
       <c r="F629" t="str">
         <v>0.000</v>
@@ -24286,7 +24286,7 @@
         <v>COILS</v>
       </c>
       <c r="H629" t="str">
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="I629" t="str">
         <v>2</v>
@@ -24298,24 +24298,24 @@
         <v>NO</v>
       </c>
       <c r="L629" t="str">
-        <v>1.450</v>
+        <v>1.550</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>D0145703</v>
+        <v>D0143676</v>
       </c>
       <c r="B630" t="str">
-        <v>810</v>
+        <v>700</v>
       </c>
       <c r="C630" t="str">
         <v>441AR</v>
       </c>
       <c r="D630" t="str">
-        <v>0.71</v>
+        <v>0.61</v>
       </c>
       <c r="E630" t="str">
-        <v>380.000</v>
+        <v>1270.000</v>
       </c>
       <c r="F630" t="str">
         <v>0.000</v>
@@ -24324,7 +24324,7 @@
         <v>COILS</v>
       </c>
       <c r="H630" t="str">
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="I630" t="str">
         <v>2</v>
@@ -24336,7 +24336,7 @@
         <v>NO</v>
       </c>
       <c r="L630" t="str">
-        <v>1.550</v>
+        <v>1.450</v>
       </c>
     </row>
     <row r="631">
@@ -24949,19 +24949,19 @@
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>D0149325</v>
+        <v>C0995190</v>
       </c>
       <c r="B647" t="str">
-        <v>2.220</v>
+        <v>1.630</v>
       </c>
       <c r="C647" t="str">
         <v>441AR</v>
       </c>
       <c r="D647" t="str">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="E647" t="str">
-        <v>1250.000</v>
+        <v>390.000</v>
       </c>
       <c r="F647" t="str">
         <v>0.000</v>
@@ -24973,7 +24973,7 @@
         <v>R</v>
       </c>
       <c r="I647" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J647" t="str">
         <v>2B</v>
@@ -24982,24 +24982,24 @@
         <v>NO</v>
       </c>
       <c r="L647" t="str">
-        <v>1.650</v>
+        <v>1.600</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>C0995190</v>
+        <v>D0149325</v>
       </c>
       <c r="B648" t="str">
-        <v>1.630</v>
+        <v>2.220</v>
       </c>
       <c r="C648" t="str">
         <v>441AR</v>
       </c>
       <c r="D648" t="str">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="E648" t="str">
-        <v>390.000</v>
+        <v>1250.000</v>
       </c>
       <c r="F648" t="str">
         <v>0.000</v>
@@ -25011,7 +25011,7 @@
         <v>R</v>
       </c>
       <c r="I648" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J648" t="str">
         <v>2B</v>
@@ -25020,7 +25020,7 @@
         <v>NO</v>
       </c>
       <c r="L648" t="str">
-        <v>1.600</v>
+        <v>1.650</v>
       </c>
     </row>
     <row r="649">
@@ -26431,10 +26431,10 @@
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>C0976111</v>
+        <v>C1027406</v>
       </c>
       <c r="B686" t="str">
-        <v>615</v>
+        <v>336</v>
       </c>
       <c r="C686" t="str">
         <v>441AR</v>
@@ -26443,7 +26443,7 @@
         <v>0.61</v>
       </c>
       <c r="E686" t="str">
-        <v>170.000</v>
+        <v>100.000</v>
       </c>
       <c r="F686" t="str">
         <v>0.000</v>
@@ -26469,10 +26469,10 @@
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>C1027406</v>
+        <v>C0976111</v>
       </c>
       <c r="B687" t="str">
-        <v>336</v>
+        <v>615</v>
       </c>
       <c r="C687" t="str">
         <v>441AR</v>
@@ -26481,7 +26481,7 @@
         <v>0.61</v>
       </c>
       <c r="E687" t="str">
-        <v>100.000</v>
+        <v>170.000</v>
       </c>
       <c r="F687" t="str">
         <v>0.000</v>
@@ -26507,19 +26507,19 @@
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>C1027547</v>
+        <v>D0149095</v>
       </c>
       <c r="B688" t="str">
-        <v>1.406</v>
+        <v>495</v>
       </c>
       <c r="C688" t="str">
         <v>441AR</v>
       </c>
       <c r="D688" t="str">
-        <v>1.14</v>
+        <v>0.78</v>
       </c>
       <c r="E688" t="str">
-        <v>180.000</v>
+        <v>220.000</v>
       </c>
       <c r="F688" t="str">
         <v>0.000</v>
@@ -26531,7 +26531,7 @@
         <v>R</v>
       </c>
       <c r="I688" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J688" t="str">
         <v>2B</v>
@@ -26540,24 +26540,24 @@
         <v>NO</v>
       </c>
       <c r="L688" t="str">
-        <v>1.600</v>
+        <v>1.450</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>D0149095</v>
+        <v>C1027547</v>
       </c>
       <c r="B689" t="str">
-        <v>495</v>
+        <v>1.406</v>
       </c>
       <c r="C689" t="str">
         <v>441AR</v>
       </c>
       <c r="D689" t="str">
-        <v>0.78</v>
+        <v>1.14</v>
       </c>
       <c r="E689" t="str">
-        <v>220.000</v>
+        <v>180.000</v>
       </c>
       <c r="F689" t="str">
         <v>0.000</v>
@@ -26569,7 +26569,7 @@
         <v>R</v>
       </c>
       <c r="I689" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J689" t="str">
         <v>2B</v>
@@ -26578,7 +26578,7 @@
         <v>NO</v>
       </c>
       <c r="L689" t="str">
-        <v>1.450</v>
+        <v>1.600</v>
       </c>
     </row>
     <row r="690">
@@ -28255,19 +28255,19 @@
     </row>
     <row r="734">
       <c r="A734" t="str">
-        <v>D0148998</v>
+        <v>C1028049</v>
       </c>
       <c r="B734" t="str">
-        <v>671</v>
+        <v>455</v>
       </c>
       <c r="C734" t="str">
         <v>441AR</v>
       </c>
       <c r="D734" t="str">
-        <v>0.61</v>
+        <v>1.00</v>
       </c>
       <c r="E734" t="str">
-        <v>200.000</v>
+        <v>130.000</v>
       </c>
       <c r="F734" t="str">
         <v>0.000</v>
@@ -28279,7 +28279,7 @@
         <v>R</v>
       </c>
       <c r="I734" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J734" t="str">
         <v>2B</v>
@@ -28288,24 +28288,24 @@
         <v>NO</v>
       </c>
       <c r="L734" t="str">
-        <v>1.450</v>
+        <v>1.600</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="str">
-        <v>C1028049</v>
+        <v>D0148998</v>
       </c>
       <c r="B735" t="str">
-        <v>455</v>
+        <v>671</v>
       </c>
       <c r="C735" t="str">
         <v>441AR</v>
       </c>
       <c r="D735" t="str">
-        <v>1.00</v>
+        <v>0.61</v>
       </c>
       <c r="E735" t="str">
-        <v>130.000</v>
+        <v>200.000</v>
       </c>
       <c r="F735" t="str">
         <v>0.000</v>
@@ -28317,7 +28317,7 @@
         <v>R</v>
       </c>
       <c r="I735" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J735" t="str">
         <v>2B</v>
@@ -28326,7 +28326,7 @@
         <v>NO</v>
       </c>
       <c r="L735" t="str">
-        <v>1.600</v>
+        <v>1.450</v>
       </c>
     </row>
     <row r="736">
@@ -28635,10 +28635,10 @@
     </row>
     <row r="744">
       <c r="A744" t="str">
-        <v>D0144970</v>
+        <v>C1002462</v>
       </c>
       <c r="B744" t="str">
-        <v>958</v>
+        <v>1.429</v>
       </c>
       <c r="C744" t="str">
         <v>441AR</v>
@@ -28647,7 +28647,7 @@
         <v>0.61</v>
       </c>
       <c r="E744" t="str">
-        <v>300.000</v>
+        <v>390.000</v>
       </c>
       <c r="F744" t="str">
         <v>0.000</v>
@@ -28659,7 +28659,7 @@
         <v>R</v>
       </c>
       <c r="I744" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J744" t="str">
         <v>2B</v>
@@ -28668,15 +28668,15 @@
         <v>NO</v>
       </c>
       <c r="L744" t="str">
-        <v>1.550</v>
+        <v>1.600</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="str">
-        <v>C1002462</v>
+        <v>D0144970</v>
       </c>
       <c r="B745" t="str">
-        <v>1.429</v>
+        <v>958</v>
       </c>
       <c r="C745" t="str">
         <v>441AR</v>
@@ -28685,7 +28685,7 @@
         <v>0.61</v>
       </c>
       <c r="E745" t="str">
-        <v>390.000</v>
+        <v>300.000</v>
       </c>
       <c r="F745" t="str">
         <v>0.000</v>
@@ -28697,7 +28697,7 @@
         <v>R</v>
       </c>
       <c r="I745" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J745" t="str">
         <v>2B</v>
@@ -28706,7 +28706,7 @@
         <v>NO</v>
       </c>
       <c r="L745" t="str">
-        <v>1.600</v>
+        <v>1.550</v>
       </c>
     </row>
     <row r="746">
@@ -29053,10 +29053,10 @@
     </row>
     <row r="755">
       <c r="A755" t="str">
-        <v>C0994456</v>
+        <v>C1002658</v>
       </c>
       <c r="B755" t="str">
-        <v>1.086</v>
+        <v>1.495</v>
       </c>
       <c r="C755" t="str">
         <v>441AR</v>
@@ -29065,7 +29065,7 @@
         <v>0.61</v>
       </c>
       <c r="E755" t="str">
-        <v>340.000</v>
+        <v>390.000</v>
       </c>
       <c r="F755" t="str">
         <v>0.000</v>
@@ -29091,10 +29091,10 @@
     </row>
     <row r="756">
       <c r="A756" t="str">
-        <v>C1002658</v>
+        <v>C0994456</v>
       </c>
       <c r="B756" t="str">
-        <v>1.495</v>
+        <v>1.086</v>
       </c>
       <c r="C756" t="str">
         <v>441AR</v>
@@ -29103,7 +29103,7 @@
         <v>0.61</v>
       </c>
       <c r="E756" t="str">
-        <v>390.000</v>
+        <v>340.000</v>
       </c>
       <c r="F756" t="str">
         <v>0.000</v>
@@ -29889,19 +29889,19 @@
     </row>
     <row r="777">
       <c r="A777" t="str">
-        <v>D0144222</v>
+        <v>D0149123</v>
       </c>
       <c r="B777" t="str">
-        <v>1.100</v>
+        <v>470</v>
       </c>
       <c r="C777" t="str">
         <v>441AR</v>
       </c>
       <c r="D777" t="str">
-        <v>0.61</v>
+        <v>0.78</v>
       </c>
       <c r="E777" t="str">
-        <v>1270.000</v>
+        <v>220.000</v>
       </c>
       <c r="F777" t="str">
         <v>0.000</v>
@@ -29910,7 +29910,7 @@
         <v>COILS</v>
       </c>
       <c r="H777" t="str">
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="I777" t="str">
         <v>2</v>
@@ -29922,24 +29922,24 @@
         <v>NO</v>
       </c>
       <c r="L777" t="str">
-        <v>1.570</v>
+        <v>1.450</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="str">
-        <v>D0149123</v>
+        <v>D0144222</v>
       </c>
       <c r="B778" t="str">
-        <v>470</v>
+        <v>1.100</v>
       </c>
       <c r="C778" t="str">
         <v>441AR</v>
       </c>
       <c r="D778" t="str">
-        <v>0.78</v>
+        <v>0.61</v>
       </c>
       <c r="E778" t="str">
-        <v>220.000</v>
+        <v>1270.000</v>
       </c>
       <c r="F778" t="str">
         <v>0.000</v>
@@ -29948,7 +29948,7 @@
         <v>COILS</v>
       </c>
       <c r="H778" t="str">
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="I778" t="str">
         <v>2</v>
@@ -29960,7 +29960,7 @@
         <v>NO</v>
       </c>
       <c r="L778" t="str">
-        <v>1.450</v>
+        <v>1.570</v>
       </c>
     </row>
     <row r="779">
@@ -30193,19 +30193,19 @@
     </row>
     <row r="785">
       <c r="A785" t="str">
-        <v>D0149850</v>
+        <v>C1002438</v>
       </c>
       <c r="B785" t="str">
-        <v>446</v>
+        <v>1.168</v>
       </c>
       <c r="C785" t="str">
         <v>441AR</v>
       </c>
       <c r="D785" t="str">
-        <v>0.82</v>
+        <v>1.00</v>
       </c>
       <c r="E785" t="str">
-        <v>215.000</v>
+        <v>150.000</v>
       </c>
       <c r="F785" t="str">
         <v>0.000</v>
@@ -30217,7 +30217,7 @@
         <v>R</v>
       </c>
       <c r="I785" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J785" t="str">
         <v>2B</v>
@@ -30226,24 +30226,24 @@
         <v>NO</v>
       </c>
       <c r="L785" t="str">
-        <v>1.450</v>
+        <v>1.600</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="str">
-        <v>C1002438</v>
+        <v>D0149850</v>
       </c>
       <c r="B786" t="str">
-        <v>1.168</v>
+        <v>446</v>
       </c>
       <c r="C786" t="str">
         <v>441AR</v>
       </c>
       <c r="D786" t="str">
-        <v>1.00</v>
+        <v>0.82</v>
       </c>
       <c r="E786" t="str">
-        <v>150.000</v>
+        <v>215.000</v>
       </c>
       <c r="F786" t="str">
         <v>0.000</v>
@@ -30255,7 +30255,7 @@
         <v>R</v>
       </c>
       <c r="I786" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J786" t="str">
         <v>2B</v>
@@ -30264,7 +30264,7 @@
         <v>NO</v>
       </c>
       <c r="L786" t="str">
-        <v>1.600</v>
+        <v>1.450</v>
       </c>
     </row>
     <row r="787">
@@ -30459,19 +30459,19 @@
     </row>
     <row r="792">
       <c r="A792" t="str">
-        <v>C0967662</v>
+        <v>C0982453</v>
       </c>
       <c r="B792" t="str">
-        <v>1.135</v>
+        <v>318</v>
       </c>
       <c r="C792" t="str">
         <v>441AR</v>
       </c>
       <c r="D792" t="str">
-        <v>0.61</v>
+        <v>1.98</v>
       </c>
       <c r="E792" t="str">
-        <v>300.000</v>
+        <v>78.500</v>
       </c>
       <c r="F792" t="str">
         <v>0.000</v>
@@ -30497,19 +30497,19 @@
     </row>
     <row r="793">
       <c r="A793" t="str">
-        <v>C0982453</v>
+        <v>C0967662</v>
       </c>
       <c r="B793" t="str">
-        <v>318</v>
+        <v>1.135</v>
       </c>
       <c r="C793" t="str">
         <v>441AR</v>
       </c>
       <c r="D793" t="str">
-        <v>1.98</v>
+        <v>0.61</v>
       </c>
       <c r="E793" t="str">
-        <v>78.500</v>
+        <v>300.000</v>
       </c>
       <c r="F793" t="str">
         <v>0.000</v>
@@ -32131,19 +32131,19 @@
     </row>
     <row r="836">
       <c r="A836" t="str">
-        <v>C0994712</v>
+        <v>D0147889</v>
       </c>
       <c r="B836" t="str">
-        <v>998</v>
+        <v>1.295</v>
       </c>
       <c r="C836" t="str">
         <v>444</v>
       </c>
       <c r="D836" t="str">
-        <v>1.50</v>
+        <v>0.50</v>
       </c>
       <c r="E836" t="str">
-        <v>130.000</v>
+        <v>190.000</v>
       </c>
       <c r="F836" t="str">
         <v>0.000</v>
@@ -32155,7 +32155,7 @@
         <v>R</v>
       </c>
       <c r="I836" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J836" t="str">
         <v>2B</v>
@@ -32164,24 +32164,24 @@
         <v>NO</v>
       </c>
       <c r="L836" t="str">
-        <v>2.100</v>
+        <v>2.150</v>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="str">
-        <v>D0147889</v>
+        <v>C0994712</v>
       </c>
       <c r="B837" t="str">
-        <v>1.295</v>
+        <v>998</v>
       </c>
       <c r="C837" t="str">
         <v>444</v>
       </c>
       <c r="D837" t="str">
-        <v>0.50</v>
+        <v>1.50</v>
       </c>
       <c r="E837" t="str">
-        <v>190.000</v>
+        <v>130.000</v>
       </c>
       <c r="F837" t="str">
         <v>0.000</v>
@@ -32193,7 +32193,7 @@
         <v>R</v>
       </c>
       <c r="I837" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J837" t="str">
         <v>2B</v>
@@ -32202,7 +32202,7 @@
         <v>NO</v>
       </c>
       <c r="L837" t="str">
-        <v>2.150</v>
+        <v>2.100</v>
       </c>
     </row>
     <row r="838">
@@ -35741,10 +35741,10 @@
     </row>
     <row r="931">
       <c r="A931" t="str">
-        <v>C0992428</v>
+        <v>C0976197</v>
       </c>
       <c r="B931" t="str">
-        <v>486</v>
+        <v>500</v>
       </c>
       <c r="C931" t="str">
         <v>4513M</v>
@@ -35753,7 +35753,7 @@
         <v>0.81</v>
       </c>
       <c r="E931" t="str">
-        <v>100.000</v>
+        <v>103.000</v>
       </c>
       <c r="F931" t="str">
         <v>0.000</v>
@@ -35779,10 +35779,10 @@
     </row>
     <row r="932">
       <c r="A932" t="str">
-        <v>C0976197</v>
+        <v>C0992428</v>
       </c>
       <c r="B932" t="str">
-        <v>500</v>
+        <v>486</v>
       </c>
       <c r="C932" t="str">
         <v>4513M</v>
@@ -35791,7 +35791,7 @@
         <v>0.81</v>
       </c>
       <c r="E932" t="str">
-        <v>103.000</v>
+        <v>100.000</v>
       </c>
       <c r="F932" t="str">
         <v>0.000</v>
@@ -37147,10 +37147,10 @@
     </row>
     <row r="968">
       <c r="A968" t="str">
-        <v>C1002460</v>
+        <v>C1010800</v>
       </c>
       <c r="B968" t="str">
-        <v>782</v>
+        <v>2.026</v>
       </c>
       <c r="C968" t="str">
         <v>4828</v>
@@ -37159,7 +37159,7 @@
         <v>1.98</v>
       </c>
       <c r="E968" t="str">
-        <v>145.000</v>
+        <v>350.000</v>
       </c>
       <c r="F968" t="str">
         <v>0.000</v>
@@ -37185,10 +37185,10 @@
     </row>
     <row r="969">
       <c r="A969" t="str">
-        <v>C1010800</v>
+        <v>C1002460</v>
       </c>
       <c r="B969" t="str">
-        <v>2.026</v>
+        <v>782</v>
       </c>
       <c r="C969" t="str">
         <v>4828</v>
@@ -37197,7 +37197,7 @@
         <v>1.98</v>
       </c>
       <c r="E969" t="str">
-        <v>350.000</v>
+        <v>145.000</v>
       </c>
       <c r="F969" t="str">
         <v>0.000</v>
@@ -37945,19 +37945,19 @@
     </row>
     <row r="989">
       <c r="A989" t="str">
-        <v>C0997774</v>
+        <v>C1010793</v>
       </c>
       <c r="B989" t="str">
-        <v>1.226</v>
+        <v>4.792</v>
       </c>
       <c r="C989" t="str">
         <v>4828</v>
       </c>
       <c r="D989" t="str">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="E989" t="str">
-        <v>215.000</v>
+        <v>413.000</v>
       </c>
       <c r="F989" t="str">
         <v>0.000</v>
@@ -37978,24 +37978,24 @@
         <v>NO</v>
       </c>
       <c r="L989" t="str">
-        <v>2.850</v>
+        <v>3.050</v>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="str">
-        <v>C1010793</v>
+        <v>C0997774</v>
       </c>
       <c r="B990" t="str">
-        <v>4.792</v>
+        <v>1.226</v>
       </c>
       <c r="C990" t="str">
         <v>4828</v>
       </c>
       <c r="D990" t="str">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="E990" t="str">
-        <v>413.000</v>
+        <v>215.000</v>
       </c>
       <c r="F990" t="str">
         <v>0.000</v>
@@ -38016,7 +38016,7 @@
         <v>NO</v>
       </c>
       <c r="L990" t="str">
-        <v>3.050</v>
+        <v>2.850</v>
       </c>
     </row>
     <row r="991">
@@ -38135,10 +38135,10 @@
     </row>
     <row r="994">
       <c r="A994" t="str">
-        <v>C0991076</v>
+        <v>C0975987</v>
       </c>
       <c r="B994" t="str">
-        <v>648</v>
+        <v>568</v>
       </c>
       <c r="C994" t="str">
         <v>4828</v>
@@ -38147,7 +38147,7 @@
         <v>1.98</v>
       </c>
       <c r="E994" t="str">
-        <v>115.000</v>
+        <v>110.000</v>
       </c>
       <c r="F994" t="str">
         <v>0.000</v>
@@ -38173,10 +38173,10 @@
     </row>
     <row r="995">
       <c r="A995" t="str">
-        <v>C0975987</v>
+        <v>C0991076</v>
       </c>
       <c r="B995" t="str">
-        <v>568</v>
+        <v>648</v>
       </c>
       <c r="C995" t="str">
         <v>4828</v>
@@ -38185,7 +38185,7 @@
         <v>1.98</v>
       </c>
       <c r="E995" t="str">
-        <v>110.000</v>
+        <v>115.000</v>
       </c>
       <c r="F995" t="str">
         <v>0.000</v>
@@ -39237,10 +39237,10 @@
     </row>
     <row r="1023">
       <c r="A1023" t="str">
-        <v>C0997671</v>
+        <v>C0976248</v>
       </c>
       <c r="B1023" t="str">
-        <v>980</v>
+        <v>679</v>
       </c>
       <c r="C1023" t="str">
         <v>4828</v>
@@ -39249,7 +39249,7 @@
         <v>1.98</v>
       </c>
       <c r="E1023" t="str">
-        <v>130.000</v>
+        <v>140.000</v>
       </c>
       <c r="F1023" t="str">
         <v>0.000</v>
@@ -39275,10 +39275,10 @@
     </row>
     <row r="1024">
       <c r="A1024" t="str">
-        <v>C0976248</v>
+        <v>C0997671</v>
       </c>
       <c r="B1024" t="str">
-        <v>679</v>
+        <v>980</v>
       </c>
       <c r="C1024" t="str">
         <v>4828</v>
@@ -39287,7 +39287,7 @@
         <v>1.98</v>
       </c>
       <c r="E1024" t="str">
-        <v>140.000</v>
+        <v>130.000</v>
       </c>
       <c r="F1024" t="str">
         <v>0.000</v>
@@ -39769,19 +39769,19 @@
     </row>
     <row r="1037">
       <c r="A1037" t="str">
-        <v>C0991233</v>
+        <v>C0986681</v>
       </c>
       <c r="B1037" t="str">
-        <v>626</v>
+        <v>502</v>
       </c>
       <c r="C1037" t="str">
         <v>4828</v>
       </c>
       <c r="D1037" t="str">
-        <v>2.48</v>
+        <v>1.98</v>
       </c>
       <c r="E1037" t="str">
-        <v>90.000</v>
+        <v>94.000</v>
       </c>
       <c r="F1037" t="str">
         <v>0.000</v>
@@ -39807,19 +39807,19 @@
     </row>
     <row r="1038">
       <c r="A1038" t="str">
-        <v>C0986681</v>
+        <v>C0991233</v>
       </c>
       <c r="B1038" t="str">
-        <v>502</v>
+        <v>626</v>
       </c>
       <c r="C1038" t="str">
         <v>4828</v>
       </c>
       <c r="D1038" t="str">
-        <v>1.98</v>
+        <v>2.48</v>
       </c>
       <c r="E1038" t="str">
-        <v>94.000</v>
+        <v>90.000</v>
       </c>
       <c r="F1038" t="str">
         <v>0.000</v>
@@ -40225,19 +40225,19 @@
     </row>
     <row r="1049">
       <c r="A1049" t="str">
-        <v>D0143206</v>
+        <v>C1009173</v>
       </c>
       <c r="B1049" t="str">
-        <v>2.619</v>
+        <v>1.850</v>
       </c>
       <c r="C1049" t="str">
         <v>4828</v>
       </c>
       <c r="D1049" t="str">
-        <v>1.98</v>
+        <v>2.58</v>
       </c>
       <c r="E1049" t="str">
-        <v>1522.000</v>
+        <v>249.000</v>
       </c>
       <c r="F1049" t="str">
         <v>0.000</v>
@@ -40246,10 +40246,10 @@
         <v>COILS</v>
       </c>
       <c r="H1049" t="str">
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="I1049" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J1049" t="str">
         <v>2B</v>
@@ -40258,24 +40258,24 @@
         <v>NO</v>
       </c>
       <c r="L1049" t="str">
-        <v>2.750</v>
+        <v>2.850</v>
       </c>
     </row>
     <row r="1050">
       <c r="A1050" t="str">
-        <v>C1009173</v>
+        <v>C0997673</v>
       </c>
       <c r="B1050" t="str">
-        <v>1.850</v>
+        <v>944</v>
       </c>
       <c r="C1050" t="str">
         <v>4828</v>
       </c>
       <c r="D1050" t="str">
-        <v>2.58</v>
+        <v>1.98</v>
       </c>
       <c r="E1050" t="str">
-        <v>249.000</v>
+        <v>130.000</v>
       </c>
       <c r="F1050" t="str">
         <v>0.000</v>
@@ -40301,10 +40301,10 @@
     </row>
     <row r="1051">
       <c r="A1051" t="str">
-        <v>C0997673</v>
+        <v>D0143206</v>
       </c>
       <c r="B1051" t="str">
-        <v>944</v>
+        <v>2.619</v>
       </c>
       <c r="C1051" t="str">
         <v>4828</v>
@@ -40313,7 +40313,7 @@
         <v>1.98</v>
       </c>
       <c r="E1051" t="str">
-        <v>130.000</v>
+        <v>1522.000</v>
       </c>
       <c r="F1051" t="str">
         <v>0.000</v>
@@ -40322,10 +40322,10 @@
         <v>COILS</v>
       </c>
       <c r="H1051" t="str">
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="I1051" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1051" t="str">
         <v>2B</v>
@@ -40334,7 +40334,7 @@
         <v>NO</v>
       </c>
       <c r="L1051" t="str">
-        <v>2.850</v>
+        <v>2.750</v>
       </c>
     </row>
     <row r="1052">
@@ -40605,10 +40605,10 @@
     </row>
     <row r="1059">
       <c r="A1059" t="str">
-        <v>D0148103</v>
+        <v>C0991083</v>
       </c>
       <c r="B1059" t="str">
-        <v>1.094</v>
+        <v>470</v>
       </c>
       <c r="C1059" t="str">
         <v>4828</v>
@@ -40617,7 +40617,7 @@
         <v>1.98</v>
       </c>
       <c r="E1059" t="str">
-        <v>1272.000</v>
+        <v>115.000</v>
       </c>
       <c r="F1059" t="str">
         <v>0.000</v>
@@ -40626,10 +40626,10 @@
         <v>COILS</v>
       </c>
       <c r="H1059" t="str">
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="I1059" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J1059" t="str">
         <v>2B</v>
@@ -40638,15 +40638,15 @@
         <v>NO</v>
       </c>
       <c r="L1059" t="str">
-        <v>2.650</v>
+        <v>2.850</v>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="str">
-        <v>C0991083</v>
+        <v>D0148103</v>
       </c>
       <c r="B1060" t="str">
-        <v>470</v>
+        <v>1.094</v>
       </c>
       <c r="C1060" t="str">
         <v>4828</v>
@@ -40655,7 +40655,7 @@
         <v>1.98</v>
       </c>
       <c r="E1060" t="str">
-        <v>115.000</v>
+        <v>1272.000</v>
       </c>
       <c r="F1060" t="str">
         <v>0.000</v>
@@ -40664,10 +40664,10 @@
         <v>COILS</v>
       </c>
       <c r="H1060" t="str">
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="I1060" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1060" t="str">
         <v>2B</v>
@@ -40676,24 +40676,24 @@
         <v>NO</v>
       </c>
       <c r="L1060" t="str">
-        <v>2.850</v>
+        <v>2.650</v>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="str">
-        <v>D0145203</v>
+        <v>D0143281</v>
       </c>
       <c r="B1061" t="str">
-        <v>4.670</v>
+        <v>4.204</v>
       </c>
       <c r="C1061" t="str">
         <v>4828</v>
       </c>
       <c r="D1061" t="str">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="E1061" t="str">
-        <v>1532.000</v>
+        <v>520.000</v>
       </c>
       <c r="F1061" t="str">
         <v>0.000</v>
@@ -40702,7 +40702,7 @@
         <v>COILS</v>
       </c>
       <c r="H1061" t="str">
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="I1061" t="str">
         <v>2</v>
@@ -40719,19 +40719,19 @@
     </row>
     <row r="1062">
       <c r="A1062" t="str">
-        <v>D0143281</v>
+        <v>D0145203</v>
       </c>
       <c r="B1062" t="str">
-        <v>4.204</v>
+        <v>4.670</v>
       </c>
       <c r="C1062" t="str">
         <v>4828</v>
       </c>
       <c r="D1062" t="str">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="E1062" t="str">
-        <v>520.000</v>
+        <v>1532.000</v>
       </c>
       <c r="F1062" t="str">
         <v>0.000</v>
@@ -40740,7 +40740,7 @@
         <v>COILS</v>
       </c>
       <c r="H1062" t="str">
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="I1062" t="str">
         <v>2</v>
@@ -43113,10 +43113,10 @@
     </row>
     <row r="1125">
       <c r="A1125" t="str">
-        <v>C1004122</v>
+        <v>D0147096</v>
       </c>
       <c r="B1125" t="str">
-        <v>1.459</v>
+        <v>2.220</v>
       </c>
       <c r="C1125" t="str">
         <v>4828</v>
@@ -43125,7 +43125,7 @@
         <v>1.98</v>
       </c>
       <c r="E1125" t="str">
-        <v>255.500</v>
+        <v>380.000</v>
       </c>
       <c r="F1125" t="str">
         <v>0.000</v>
@@ -43137,7 +43137,7 @@
         <v>R</v>
       </c>
       <c r="I1125" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1125" t="str">
         <v>2B</v>
@@ -43146,15 +43146,15 @@
         <v>NO</v>
       </c>
       <c r="L1125" t="str">
-        <v>2.850</v>
+        <v>2.750</v>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="str">
-        <v>D0147096</v>
+        <v>C1004122</v>
       </c>
       <c r="B1126" t="str">
-        <v>2.220</v>
+        <v>1.459</v>
       </c>
       <c r="C1126" t="str">
         <v>4828</v>
@@ -43163,7 +43163,7 @@
         <v>1.98</v>
       </c>
       <c r="E1126" t="str">
-        <v>380.000</v>
+        <v>255.500</v>
       </c>
       <c r="F1126" t="str">
         <v>0.000</v>
@@ -43175,7 +43175,7 @@
         <v>R</v>
       </c>
       <c r="I1126" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J1126" t="str">
         <v>2B</v>
@@ -43184,7 +43184,7 @@
         <v>NO</v>
       </c>
       <c r="L1126" t="str">
-        <v>2.750</v>
+        <v>2.850</v>
       </c>
     </row>
     <row r="1127">
@@ -44177,19 +44177,19 @@
     </row>
     <row r="1153">
       <c r="A1153" t="str">
-        <v>D0149782</v>
+        <v>C1011397</v>
       </c>
       <c r="B1153" t="str">
-        <v>1.720</v>
+        <v>2.350</v>
       </c>
       <c r="C1153" t="str">
         <v>304DL</v>
       </c>
       <c r="D1153" t="str">
-        <v>4.97</v>
+        <v>1.50</v>
       </c>
       <c r="E1153" t="str">
-        <v>1250.000</v>
+        <v>1277.000</v>
       </c>
       <c r="F1153" t="str">
         <v>0.000</v>
@@ -44198,10 +44198,10 @@
         <v>COILS</v>
       </c>
       <c r="H1153" t="str">
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="I1153" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J1153" t="str">
         <v>2B</v>
@@ -44210,24 +44210,24 @@
         <v>NO</v>
       </c>
       <c r="L1153" t="str">
-        <v>2.250</v>
+        <v>2.350</v>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="str">
-        <v>C1011397</v>
+        <v>D0149782</v>
       </c>
       <c r="B1154" t="str">
-        <v>2.350</v>
+        <v>1.720</v>
       </c>
       <c r="C1154" t="str">
         <v>304DL</v>
       </c>
       <c r="D1154" t="str">
-        <v>1.50</v>
+        <v>4.97</v>
       </c>
       <c r="E1154" t="str">
-        <v>1277.000</v>
+        <v>1250.000</v>
       </c>
       <c r="F1154" t="str">
         <v>0.000</v>
@@ -44236,10 +44236,10 @@
         <v>COILS</v>
       </c>
       <c r="H1154" t="str">
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="I1154" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1154" t="str">
         <v>2B</v>
@@ -44248,7 +44248,7 @@
         <v>NO</v>
       </c>
       <c r="L1154" t="str">
-        <v>2.350</v>
+        <v>2.250</v>
       </c>
     </row>
     <row r="1155">
@@ -44329,19 +44329,19 @@
     </row>
     <row r="1157">
       <c r="A1157" t="str">
-        <v>D0149733</v>
+        <v>C1008774</v>
       </c>
       <c r="B1157" t="str">
-        <v>1.400</v>
+        <v>447</v>
       </c>
       <c r="C1157" t="str">
         <v>304DL</v>
       </c>
       <c r="D1157" t="str">
-        <v>1.47</v>
+        <v>0.81</v>
       </c>
       <c r="E1157" t="str">
-        <v>1277.000</v>
+        <v>110.000</v>
       </c>
       <c r="F1157" t="str">
         <v>0.000</v>
@@ -44350,10 +44350,10 @@
         <v>COILS</v>
       </c>
       <c r="H1157" t="str">
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="I1157" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J1157" t="str">
         <v>2B</v>
@@ -44362,7 +44362,7 @@
         <v>NO</v>
       </c>
       <c r="L1157" t="str">
-        <v>2.250</v>
+        <v>2.350</v>
       </c>
     </row>
     <row r="1158">
@@ -44405,19 +44405,19 @@
     </row>
     <row r="1159">
       <c r="A1159" t="str">
-        <v>C1008774</v>
+        <v>D0149733</v>
       </c>
       <c r="B1159" t="str">
-        <v>447</v>
+        <v>1.400</v>
       </c>
       <c r="C1159" t="str">
         <v>304DL</v>
       </c>
       <c r="D1159" t="str">
-        <v>0.81</v>
+        <v>1.47</v>
       </c>
       <c r="E1159" t="str">
-        <v>110.000</v>
+        <v>1277.000</v>
       </c>
       <c r="F1159" t="str">
         <v>0.000</v>
@@ -44426,10 +44426,10 @@
         <v>COILS</v>
       </c>
       <c r="H1159" t="str">
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="I1159" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1159" t="str">
         <v>2B</v>
@@ -44438,33 +44438,33 @@
         <v>NO</v>
       </c>
       <c r="L1159" t="str">
-        <v>2.350</v>
+        <v>2.250</v>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="str">
-        <v>D0148718</v>
+        <v>D0149635</v>
       </c>
       <c r="B1160" t="str">
-        <v>1.050</v>
+        <v>3.700</v>
       </c>
       <c r="C1160" t="str">
         <v>304DL</v>
       </c>
       <c r="D1160" t="str">
-        <v>4.94</v>
+        <v>2.48</v>
       </c>
       <c r="E1160" t="str">
-        <v>1500.000</v>
+        <v>1522.000</v>
       </c>
       <c r="F1160" t="str">
-        <v>3000.000</v>
+        <v>0.000</v>
       </c>
       <c r="G1160" t="str">
-        <v>BLANKS</v>
+        <v>COILS</v>
       </c>
       <c r="H1160" t="str">
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="I1160" t="str">
         <v>2</v>
@@ -44476,33 +44476,33 @@
         <v>NO</v>
       </c>
       <c r="L1160" t="str">
-        <v>2.650</v>
+        <v>2.350</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="str">
-        <v>D0149635</v>
+        <v>D0148718</v>
       </c>
       <c r="B1161" t="str">
-        <v>3.700</v>
+        <v>1.050</v>
       </c>
       <c r="C1161" t="str">
         <v>304DL</v>
       </c>
       <c r="D1161" t="str">
-        <v>2.48</v>
+        <v>4.94</v>
       </c>
       <c r="E1161" t="str">
-        <v>1522.000</v>
+        <v>1500.000</v>
       </c>
       <c r="F1161" t="str">
-        <v>0.000</v>
+        <v>3000.000</v>
       </c>
       <c r="G1161" t="str">
-        <v>COILS</v>
+        <v>BLANKS</v>
       </c>
       <c r="H1161" t="str">
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="I1161" t="str">
         <v>2</v>
@@ -44514,7 +44514,7 @@
         <v>NO</v>
       </c>
       <c r="L1161" t="str">
-        <v>2.350</v>
+        <v>2.650</v>
       </c>
     </row>
     <row r="1162">
@@ -45393,10 +45393,10 @@
     </row>
     <row r="1185">
       <c r="A1185" t="str">
-        <v>D0148528</v>
+        <v>D0149310</v>
       </c>
       <c r="B1185" t="str">
-        <v>1.825</v>
+        <v>7.940</v>
       </c>
       <c r="C1185" t="str">
         <v>304DL</v>
@@ -45405,7 +45405,7 @@
         <v>0.98</v>
       </c>
       <c r="E1185" t="str">
-        <v>1280.000</v>
+        <v>1522.000</v>
       </c>
       <c r="F1185" t="str">
         <v>0.000</v>
@@ -45426,15 +45426,15 @@
         <v>NO</v>
       </c>
       <c r="L1185" t="str">
-        <v>2.250</v>
+        <v>2.350</v>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="str">
-        <v>D0149310</v>
+        <v>D0148528</v>
       </c>
       <c r="B1186" t="str">
-        <v>7.940</v>
+        <v>1.825</v>
       </c>
       <c r="C1186" t="str">
         <v>304DL</v>
@@ -45443,7 +45443,7 @@
         <v>0.98</v>
       </c>
       <c r="E1186" t="str">
-        <v>1522.000</v>
+        <v>1280.000</v>
       </c>
       <c r="F1186" t="str">
         <v>0.000</v>
@@ -45464,7 +45464,7 @@
         <v>NO</v>
       </c>
       <c r="L1186" t="str">
-        <v>2.350</v>
+        <v>2.250</v>
       </c>
     </row>
     <row r="1187">
@@ -47179,19 +47179,19 @@
     </row>
     <row r="1232">
       <c r="A1232" t="str">
-        <v>D0147458</v>
+        <v>D0149822</v>
       </c>
       <c r="B1232" t="str">
-        <v>1.251</v>
+        <v>1.510</v>
       </c>
       <c r="C1232" t="str">
         <v>304DL</v>
       </c>
       <c r="D1232" t="str">
-        <v>1.00</v>
+        <v>0.81</v>
       </c>
       <c r="E1232" t="str">
-        <v>1277.000</v>
+        <v>1522.000</v>
       </c>
       <c r="F1232" t="str">
         <v>0.000</v>
@@ -47217,19 +47217,19 @@
     </row>
     <row r="1233">
       <c r="A1233" t="str">
-        <v>D0149822</v>
+        <v>D0147458</v>
       </c>
       <c r="B1233" t="str">
-        <v>1.510</v>
+        <v>1.251</v>
       </c>
       <c r="C1233" t="str">
         <v>304DL</v>
       </c>
       <c r="D1233" t="str">
-        <v>0.81</v>
+        <v>1.00</v>
       </c>
       <c r="E1233" t="str">
-        <v>1522.000</v>
+        <v>1277.000</v>
       </c>
       <c r="F1233" t="str">
         <v>0.000</v>
@@ -48357,25 +48357,25 @@
     </row>
     <row r="1263">
       <c r="A1263" t="str">
-        <v>D0149744</v>
+        <v>C1028362</v>
       </c>
       <c r="B1263" t="str">
-        <v>2.012</v>
+        <v>1.151</v>
       </c>
       <c r="C1263" t="str">
         <v>304DL</v>
       </c>
       <c r="D1263" t="str">
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="E1263" t="str">
-        <v>120.000</v>
+        <v>1250.000</v>
       </c>
       <c r="F1263" t="str">
-        <v>0.000</v>
+        <v>2500.000</v>
       </c>
       <c r="G1263" t="str">
-        <v>COILS</v>
+        <v>BLANKS</v>
       </c>
       <c r="H1263" t="str">
         <v>R</v>
@@ -48390,30 +48390,30 @@
         <v>NO</v>
       </c>
       <c r="L1263" t="str">
-        <v>2.250</v>
+        <v>2.750</v>
       </c>
     </row>
     <row r="1264">
       <c r="A1264" t="str">
-        <v>C1028362</v>
+        <v>D0149744</v>
       </c>
       <c r="B1264" t="str">
-        <v>1.151</v>
+        <v>2.012</v>
       </c>
       <c r="C1264" t="str">
         <v>304DL</v>
       </c>
       <c r="D1264" t="str">
-        <v>0.79</v>
+        <v>0.81</v>
       </c>
       <c r="E1264" t="str">
-        <v>1250.000</v>
+        <v>120.000</v>
       </c>
       <c r="F1264" t="str">
-        <v>2500.000</v>
+        <v>0.000</v>
       </c>
       <c r="G1264" t="str">
-        <v>BLANKS</v>
+        <v>COILS</v>
       </c>
       <c r="H1264" t="str">
         <v>R</v>
@@ -48428,7 +48428,7 @@
         <v>NO</v>
       </c>
       <c r="L1264" t="str">
-        <v>2.750</v>
+        <v>2.250</v>
       </c>
     </row>
     <row r="1265">
@@ -48699,16 +48699,16 @@
     </row>
     <row r="1272">
       <c r="A1272" t="str">
-        <v>D0148314</v>
+        <v>D0149232</v>
       </c>
       <c r="B1272" t="str">
-        <v>3.710</v>
+        <v>2.741</v>
       </c>
       <c r="C1272" t="str">
         <v>304DL</v>
       </c>
       <c r="D1272" t="str">
-        <v>0.79</v>
+        <v>1.00</v>
       </c>
       <c r="E1272" t="str">
         <v>1277.000</v>
@@ -48732,21 +48732,21 @@
         <v>NO</v>
       </c>
       <c r="L1272" t="str">
-        <v>2.350</v>
+        <v>2.250</v>
       </c>
     </row>
     <row r="1273">
       <c r="A1273" t="str">
-        <v>D0149232</v>
+        <v>D0148314</v>
       </c>
       <c r="B1273" t="str">
-        <v>2.741</v>
+        <v>3.710</v>
       </c>
       <c r="C1273" t="str">
         <v>304DL</v>
       </c>
       <c r="D1273" t="str">
-        <v>1.00</v>
+        <v>0.79</v>
       </c>
       <c r="E1273" t="str">
         <v>1277.000</v>
@@ -48770,7 +48770,7 @@
         <v>NO</v>
       </c>
       <c r="L1273" t="str">
-        <v>2.250</v>
+        <v>2.350</v>
       </c>
     </row>
     <row r="1274">
@@ -48813,25 +48813,25 @@
     </row>
     <row r="1275">
       <c r="A1275" t="str">
-        <v>C1027424</v>
+        <v>D0148819</v>
       </c>
       <c r="B1275" t="str">
-        <v>450</v>
+        <v>1.374</v>
       </c>
       <c r="C1275" t="str">
         <v>304DL</v>
       </c>
       <c r="D1275" t="str">
-        <v>0.50</v>
+        <v>1.50</v>
       </c>
       <c r="E1275" t="str">
-        <v>150.000</v>
+        <v>1250.000</v>
       </c>
       <c r="F1275" t="str">
-        <v>0.000</v>
+        <v>2500.000</v>
       </c>
       <c r="G1275" t="str">
-        <v>COILS</v>
+        <v>BLANKS</v>
       </c>
       <c r="H1275" t="str">
         <v>R</v>
@@ -48846,30 +48846,30 @@
         <v>NO</v>
       </c>
       <c r="L1275" t="str">
-        <v>2.250</v>
+        <v>2.750</v>
       </c>
     </row>
     <row r="1276">
       <c r="A1276" t="str">
-        <v>D0148819</v>
+        <v>C1027424</v>
       </c>
       <c r="B1276" t="str">
-        <v>1.374</v>
+        <v>450</v>
       </c>
       <c r="C1276" t="str">
         <v>304DL</v>
       </c>
       <c r="D1276" t="str">
-        <v>1.50</v>
+        <v>0.50</v>
       </c>
       <c r="E1276" t="str">
-        <v>1250.000</v>
+        <v>150.000</v>
       </c>
       <c r="F1276" t="str">
-        <v>2500.000</v>
+        <v>0.000</v>
       </c>
       <c r="G1276" t="str">
-        <v>BLANKS</v>
+        <v>COILS</v>
       </c>
       <c r="H1276" t="str">
         <v>R</v>
@@ -48884,7 +48884,7 @@
         <v>NO</v>
       </c>
       <c r="L1276" t="str">
-        <v>2.750</v>
+        <v>2.250</v>
       </c>
     </row>
     <row r="1277">
@@ -49155,16 +49155,16 @@
     </row>
     <row r="1284">
       <c r="A1284" t="str">
-        <v>D0149644</v>
+        <v>D0149314</v>
       </c>
       <c r="B1284" t="str">
-        <v>2.130</v>
+        <v>2.790</v>
       </c>
       <c r="C1284" t="str">
         <v>304DL</v>
       </c>
       <c r="D1284" t="str">
-        <v>0.81</v>
+        <v>1.98</v>
       </c>
       <c r="E1284" t="str">
         <v>1277.000</v>
@@ -49193,16 +49193,16 @@
     </row>
     <row r="1285">
       <c r="A1285" t="str">
-        <v>D0149314</v>
+        <v>D0149644</v>
       </c>
       <c r="B1285" t="str">
-        <v>2.790</v>
+        <v>2.130</v>
       </c>
       <c r="C1285" t="str">
         <v>304DL</v>
       </c>
       <c r="D1285" t="str">
-        <v>1.98</v>
+        <v>0.81</v>
       </c>
       <c r="E1285" t="str">
         <v>1277.000</v>
@@ -49725,19 +49725,19 @@
     </row>
     <row r="1299">
       <c r="A1299" t="str">
-        <v>D0149808</v>
+        <v>D0149012</v>
       </c>
       <c r="B1299" t="str">
-        <v>1.693</v>
+        <v>2.825</v>
       </c>
       <c r="C1299" t="str">
         <v>304DL</v>
       </c>
       <c r="D1299" t="str">
-        <v>0.61</v>
+        <v>1.00</v>
       </c>
       <c r="E1299" t="str">
-        <v>220.000</v>
+        <v>1277.000</v>
       </c>
       <c r="F1299" t="str">
         <v>0.000</v>
@@ -49746,7 +49746,7 @@
         <v>COILS</v>
       </c>
       <c r="H1299" t="str">
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="I1299" t="str">
         <v>2</v>
@@ -49758,24 +49758,24 @@
         <v>NO</v>
       </c>
       <c r="L1299" t="str">
-        <v>2.350</v>
+        <v>2.250</v>
       </c>
     </row>
     <row r="1300">
       <c r="A1300" t="str">
-        <v>D0149012</v>
+        <v>D0149808</v>
       </c>
       <c r="B1300" t="str">
-        <v>2.825</v>
+        <v>1.693</v>
       </c>
       <c r="C1300" t="str">
         <v>304DL</v>
       </c>
       <c r="D1300" t="str">
-        <v>1.00</v>
+        <v>0.61</v>
       </c>
       <c r="E1300" t="str">
-        <v>1277.000</v>
+        <v>220.000</v>
       </c>
       <c r="F1300" t="str">
         <v>0.000</v>
@@ -49784,7 +49784,7 @@
         <v>COILS</v>
       </c>
       <c r="H1300" t="str">
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="I1300" t="str">
         <v>2</v>
@@ -49796,7 +49796,7 @@
         <v>NO</v>
       </c>
       <c r="L1300" t="str">
-        <v>2.250</v>
+        <v>2.350</v>
       </c>
     </row>
     <row r="1301">
@@ -50333,28 +50333,28 @@
     </row>
     <row r="1315">
       <c r="A1315" t="str">
-        <v>D0148847</v>
+        <v>D0143261</v>
       </c>
       <c r="B1315" t="str">
-        <v>1.575</v>
+        <v>790</v>
       </c>
       <c r="C1315" t="str">
         <v>304DL</v>
       </c>
       <c r="D1315" t="str">
-        <v>4.97</v>
+        <v>0.78</v>
       </c>
       <c r="E1315" t="str">
-        <v>1500.000</v>
+        <v>1277.000</v>
       </c>
       <c r="F1315" t="str">
-        <v>3000.000</v>
+        <v>0.000</v>
       </c>
       <c r="G1315" t="str">
-        <v>BLANKS</v>
+        <v>COILS</v>
       </c>
       <c r="H1315" t="str">
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="I1315" t="str">
         <v>2</v>
@@ -50366,33 +50366,33 @@
         <v>NO</v>
       </c>
       <c r="L1315" t="str">
-        <v>2.750</v>
+        <v>2.250</v>
       </c>
     </row>
     <row r="1316">
       <c r="A1316" t="str">
-        <v>D0143261</v>
+        <v>D0148847</v>
       </c>
       <c r="B1316" t="str">
-        <v>790</v>
+        <v>1.575</v>
       </c>
       <c r="C1316" t="str">
         <v>304DL</v>
       </c>
       <c r="D1316" t="str">
-        <v>0.78</v>
+        <v>4.97</v>
       </c>
       <c r="E1316" t="str">
-        <v>1277.000</v>
+        <v>1500.000</v>
       </c>
       <c r="F1316" t="str">
-        <v>0.000</v>
+        <v>3000.000</v>
       </c>
       <c r="G1316" t="str">
-        <v>COILS</v>
+        <v>BLANKS</v>
       </c>
       <c r="H1316" t="str">
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="I1316" t="str">
         <v>2</v>
@@ -50404,7 +50404,7 @@
         <v>NO</v>
       </c>
       <c r="L1316" t="str">
-        <v>2.250</v>
+        <v>2.750</v>
       </c>
     </row>
     <row r="1317">
@@ -51435,28 +51435,28 @@
     </row>
     <row r="1344">
       <c r="A1344" t="str">
-        <v>D0148987</v>
+        <v>D0149175</v>
       </c>
       <c r="B1344" t="str">
-        <v>1.255</v>
+        <v>1.232</v>
       </c>
       <c r="C1344" t="str">
         <v>304DL</v>
       </c>
       <c r="D1344" t="str">
-        <v>2.97</v>
+        <v>1.00</v>
       </c>
       <c r="E1344" t="str">
-        <v>1500.000</v>
+        <v>1000.000</v>
       </c>
       <c r="F1344" t="str">
-        <v>3000.000</v>
+        <v>2000.000</v>
       </c>
       <c r="G1344" t="str">
         <v>BLANKS</v>
       </c>
       <c r="H1344" t="str">
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="I1344" t="str">
         <v>2</v>
@@ -51473,28 +51473,28 @@
     </row>
     <row r="1345">
       <c r="A1345" t="str">
-        <v>D0149175</v>
+        <v>D0148987</v>
       </c>
       <c r="B1345" t="str">
-        <v>1.232</v>
+        <v>1.255</v>
       </c>
       <c r="C1345" t="str">
         <v>304DL</v>
       </c>
       <c r="D1345" t="str">
-        <v>1.00</v>
+        <v>2.97</v>
       </c>
       <c r="E1345" t="str">
-        <v>1000.000</v>
+        <v>1500.000</v>
       </c>
       <c r="F1345" t="str">
-        <v>2000.000</v>
+        <v>3000.000</v>
       </c>
       <c r="G1345" t="str">
         <v>BLANKS</v>
       </c>
       <c r="H1345" t="str">
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="I1345" t="str">
         <v>2</v>
@@ -51587,22 +51587,22 @@
     </row>
     <row r="1348">
       <c r="A1348" t="str">
-        <v>C1027584</v>
+        <v>C1027276</v>
       </c>
       <c r="B1348" t="str">
-        <v>1.166</v>
+        <v>804</v>
       </c>
       <c r="C1348" t="str">
         <v>304DL</v>
       </c>
       <c r="D1348" t="str">
-        <v>0.70</v>
+        <v>0.60</v>
       </c>
       <c r="E1348" t="str">
-        <v>1500.000</v>
+        <v>665.000</v>
       </c>
       <c r="F1348" t="str">
-        <v>3000.000</v>
+        <v>1458.000</v>
       </c>
       <c r="G1348" t="str">
         <v>BLANKS</v>
@@ -51617,30 +51617,30 @@
         <v>2B</v>
       </c>
       <c r="K1348" t="str">
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="L1348" t="str">
-        <v>2.850</v>
+        <v>2.550</v>
       </c>
     </row>
     <row r="1349">
       <c r="A1349" t="str">
-        <v>C1027276</v>
+        <v>C1027584</v>
       </c>
       <c r="B1349" t="str">
-        <v>804</v>
+        <v>1.166</v>
       </c>
       <c r="C1349" t="str">
         <v>304DL</v>
       </c>
       <c r="D1349" t="str">
-        <v>0.60</v>
+        <v>0.70</v>
       </c>
       <c r="E1349" t="str">
-        <v>665.000</v>
+        <v>1500.000</v>
       </c>
       <c r="F1349" t="str">
-        <v>1458.000</v>
+        <v>3000.000</v>
       </c>
       <c r="G1349" t="str">
         <v>BLANKS</v>
@@ -51655,10 +51655,10 @@
         <v>2B</v>
       </c>
       <c r="K1349" t="str">
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="L1349" t="str">
-        <v>2.550</v>
+        <v>2.850</v>
       </c>
     </row>
     <row r="1350">
@@ -51739,31 +51739,31 @@
     </row>
     <row r="1352">
       <c r="A1352" t="str">
-        <v>C1005307</v>
+        <v>D0148816</v>
       </c>
       <c r="B1352" t="str">
-        <v>1.400</v>
+        <v>850</v>
       </c>
       <c r="C1352" t="str">
         <v>304DL</v>
       </c>
       <c r="D1352" t="str">
-        <v>1.00</v>
+        <v>1.50</v>
       </c>
       <c r="E1352" t="str">
-        <v>1277.000</v>
+        <v>1250.000</v>
       </c>
       <c r="F1352" t="str">
-        <v>0.000</v>
+        <v>2500.000</v>
       </c>
       <c r="G1352" t="str">
-        <v>COILS</v>
+        <v>BLANKS</v>
       </c>
       <c r="H1352" t="str">
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="I1352" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1352" t="str">
         <v>2B</v>
@@ -51772,36 +51772,36 @@
         <v>NO</v>
       </c>
       <c r="L1352" t="str">
-        <v>2.350</v>
+        <v>2.750</v>
       </c>
     </row>
     <row r="1353">
       <c r="A1353" t="str">
-        <v>D0148816</v>
+        <v>C1005307</v>
       </c>
       <c r="B1353" t="str">
-        <v>850</v>
+        <v>1.400</v>
       </c>
       <c r="C1353" t="str">
         <v>304DL</v>
       </c>
       <c r="D1353" t="str">
-        <v>1.50</v>
+        <v>1.00</v>
       </c>
       <c r="E1353" t="str">
-        <v>1250.000</v>
+        <v>1277.000</v>
       </c>
       <c r="F1353" t="str">
-        <v>2500.000</v>
+        <v>0.000</v>
       </c>
       <c r="G1353" t="str">
-        <v>BLANKS</v>
+        <v>COILS</v>
       </c>
       <c r="H1353" t="str">
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="I1353" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J1353" t="str">
         <v>2B</v>
@@ -51810,7 +51810,7 @@
         <v>NO</v>
       </c>
       <c r="L1353" t="str">
-        <v>2.750</v>
+        <v>2.350</v>
       </c>
     </row>
     <row r="1354">
@@ -52005,28 +52005,28 @@
     </row>
     <row r="1359">
       <c r="A1359" t="str">
-        <v>D0149465</v>
+        <v>D0148789</v>
       </c>
       <c r="B1359" t="str">
-        <v>2.000</v>
+        <v>600</v>
       </c>
       <c r="C1359" t="str">
         <v>304DL</v>
       </c>
       <c r="D1359" t="str">
-        <v>1.47</v>
+        <v>1.20</v>
       </c>
       <c r="E1359" t="str">
-        <v>1277.000</v>
+        <v>1250.000</v>
       </c>
       <c r="F1359" t="str">
-        <v>0.000</v>
+        <v>2500.000</v>
       </c>
       <c r="G1359" t="str">
-        <v>COILS</v>
+        <v>BLANKS</v>
       </c>
       <c r="H1359" t="str">
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="I1359" t="str">
         <v>2</v>
@@ -52038,33 +52038,33 @@
         <v>NO</v>
       </c>
       <c r="L1359" t="str">
-        <v>2.250</v>
+        <v>2.650</v>
       </c>
     </row>
     <row r="1360">
       <c r="A1360" t="str">
-        <v>D0148789</v>
+        <v>D0149465</v>
       </c>
       <c r="B1360" t="str">
-        <v>600</v>
+        <v>2.000</v>
       </c>
       <c r="C1360" t="str">
         <v>304DL</v>
       </c>
       <c r="D1360" t="str">
-        <v>1.20</v>
+        <v>1.47</v>
       </c>
       <c r="E1360" t="str">
-        <v>1250.000</v>
+        <v>1277.000</v>
       </c>
       <c r="F1360" t="str">
-        <v>2500.000</v>
+        <v>0.000</v>
       </c>
       <c r="G1360" t="str">
-        <v>BLANKS</v>
+        <v>COILS</v>
       </c>
       <c r="H1360" t="str">
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="I1360" t="str">
         <v>2</v>
@@ -52076,7 +52076,7 @@
         <v>NO</v>
       </c>
       <c r="L1360" t="str">
-        <v>2.650</v>
+        <v>2.250</v>
       </c>
     </row>
     <row r="1361">
@@ -52309,25 +52309,25 @@
     </row>
     <row r="1367">
       <c r="A1367" t="str">
-        <v>C1027274</v>
+        <v>D0149805</v>
       </c>
       <c r="B1367" t="str">
-        <v>720</v>
+        <v>2.243</v>
       </c>
       <c r="C1367" t="str">
         <v>304DL</v>
       </c>
       <c r="D1367" t="str">
-        <v>1.00</v>
+        <v>1.47</v>
       </c>
       <c r="E1367" t="str">
-        <v>1000.000</v>
+        <v>310.000</v>
       </c>
       <c r="F1367" t="str">
-        <v>3000.000</v>
+        <v>0.000</v>
       </c>
       <c r="G1367" t="str">
-        <v>BLANKS</v>
+        <v>COILS</v>
       </c>
       <c r="H1367" t="str">
         <v>R</v>
@@ -52339,33 +52339,33 @@
         <v>2B</v>
       </c>
       <c r="K1367" t="str">
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="L1367" t="str">
-        <v>2.350</v>
+        <v>2.250</v>
       </c>
     </row>
     <row r="1368">
       <c r="A1368" t="str">
-        <v>D0149805</v>
+        <v>C1027274</v>
       </c>
       <c r="B1368" t="str">
-        <v>2.243</v>
+        <v>720</v>
       </c>
       <c r="C1368" t="str">
         <v>304DL</v>
       </c>
       <c r="D1368" t="str">
-        <v>1.47</v>
+        <v>1.00</v>
       </c>
       <c r="E1368" t="str">
-        <v>310.000</v>
+        <v>1000.000</v>
       </c>
       <c r="F1368" t="str">
-        <v>0.000</v>
+        <v>3000.000</v>
       </c>
       <c r="G1368" t="str">
-        <v>COILS</v>
+        <v>BLANKS</v>
       </c>
       <c r="H1368" t="str">
         <v>R</v>
@@ -52377,10 +52377,10 @@
         <v>2B</v>
       </c>
       <c r="K1368" t="str">
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="L1368" t="str">
-        <v>2.250</v>
+        <v>2.350</v>
       </c>
     </row>
     <row r="1369">
@@ -52575,19 +52575,19 @@
     </row>
     <row r="1374">
       <c r="A1374" t="str">
-        <v>D0149826</v>
+        <v>D0148395</v>
       </c>
       <c r="B1374" t="str">
-        <v>990</v>
+        <v>1.370</v>
       </c>
       <c r="C1374" t="str">
         <v>304DL</v>
       </c>
       <c r="D1374" t="str">
-        <v>1.50</v>
+        <v>1.20</v>
       </c>
       <c r="E1374" t="str">
-        <v>1110.000</v>
+        <v>1022.000</v>
       </c>
       <c r="F1374" t="str">
         <v>0.000</v>
@@ -52596,7 +52596,7 @@
         <v>COILS</v>
       </c>
       <c r="H1374" t="str">
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="I1374" t="str">
         <v>2</v>
@@ -52613,19 +52613,19 @@
     </row>
     <row r="1375">
       <c r="A1375" t="str">
-        <v>D0148395</v>
+        <v>D0149826</v>
       </c>
       <c r="B1375" t="str">
-        <v>1.370</v>
+        <v>990</v>
       </c>
       <c r="C1375" t="str">
         <v>304DL</v>
       </c>
       <c r="D1375" t="str">
-        <v>1.20</v>
+        <v>1.50</v>
       </c>
       <c r="E1375" t="str">
-        <v>1022.000</v>
+        <v>1110.000</v>
       </c>
       <c r="F1375" t="str">
         <v>0.000</v>
@@ -52634,7 +52634,7 @@
         <v>COILS</v>
       </c>
       <c r="H1375" t="str">
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="I1375" t="str">
         <v>2</v>
@@ -52689,22 +52689,22 @@
     </row>
     <row r="1377">
       <c r="A1377" t="str">
-        <v>D0149253</v>
+        <v>C1004107</v>
       </c>
       <c r="B1377" t="str">
-        <v>1.305</v>
+        <v>330</v>
       </c>
       <c r="C1377" t="str">
         <v>304DL</v>
       </c>
       <c r="D1377" t="str">
-        <v>1.47</v>
+        <v>1.50</v>
       </c>
       <c r="E1377" t="str">
-        <v>1110.000</v>
+        <v>1310.000</v>
       </c>
       <c r="F1377" t="str">
-        <v>1600.000</v>
+        <v>3000.000</v>
       </c>
       <c r="G1377" t="str">
         <v>BLANKS</v>
@@ -52713,7 +52713,7 @@
         <v>R</v>
       </c>
       <c r="I1377" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J1377" t="str">
         <v>2B</v>
@@ -52722,27 +52722,27 @@
         <v>NO</v>
       </c>
       <c r="L1377" t="str">
-        <v>2.450</v>
+        <v>2.550</v>
       </c>
     </row>
     <row r="1378">
       <c r="A1378" t="str">
-        <v>C1004107</v>
+        <v>D0149253</v>
       </c>
       <c r="B1378" t="str">
-        <v>330</v>
+        <v>1.305</v>
       </c>
       <c r="C1378" t="str">
         <v>304DL</v>
       </c>
       <c r="D1378" t="str">
-        <v>1.50</v>
+        <v>1.47</v>
       </c>
       <c r="E1378" t="str">
-        <v>1310.000</v>
+        <v>1110.000</v>
       </c>
       <c r="F1378" t="str">
-        <v>3000.000</v>
+        <v>1600.000</v>
       </c>
       <c r="G1378" t="str">
         <v>BLANKS</v>
@@ -52751,7 +52751,7 @@
         <v>R</v>
       </c>
       <c r="I1378" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1378" t="str">
         <v>2B</v>
@@ -52760,7 +52760,7 @@
         <v>NO</v>
       </c>
       <c r="L1378" t="str">
-        <v>2.550</v>
+        <v>2.450</v>
       </c>
     </row>
     <row r="1379">
@@ -52955,25 +52955,25 @@
     </row>
     <row r="1384">
       <c r="A1384" t="str">
-        <v>D0147749</v>
+        <v>D0149601</v>
       </c>
       <c r="B1384" t="str">
-        <v>1.925</v>
+        <v>1.580</v>
       </c>
       <c r="C1384" t="str">
         <v>304DL</v>
       </c>
       <c r="D1384" t="str">
-        <v>0.78</v>
+        <v>2.47</v>
       </c>
       <c r="E1384" t="str">
-        <v>110.000</v>
+        <v>1500.000</v>
       </c>
       <c r="F1384" t="str">
-        <v>0.000</v>
+        <v>3000.000</v>
       </c>
       <c r="G1384" t="str">
-        <v>COILS</v>
+        <v>BLANKS</v>
       </c>
       <c r="H1384" t="str">
         <v>R</v>
@@ -52988,30 +52988,30 @@
         <v>NO</v>
       </c>
       <c r="L1384" t="str">
-        <v>2.250</v>
+        <v>2.750</v>
       </c>
     </row>
     <row r="1385">
       <c r="A1385" t="str">
-        <v>D0149601</v>
+        <v>D0147749</v>
       </c>
       <c r="B1385" t="str">
-        <v>1.580</v>
+        <v>1.925</v>
       </c>
       <c r="C1385" t="str">
         <v>304DL</v>
       </c>
       <c r="D1385" t="str">
-        <v>2.47</v>
+        <v>0.78</v>
       </c>
       <c r="E1385" t="str">
-        <v>1500.000</v>
+        <v>110.000</v>
       </c>
       <c r="F1385" t="str">
-        <v>3000.000</v>
+        <v>0.000</v>
       </c>
       <c r="G1385" t="str">
-        <v>BLANKS</v>
+        <v>COILS</v>
       </c>
       <c r="H1385" t="str">
         <v>R</v>
@@ -53026,7 +53026,7 @@
         <v>NO</v>
       </c>
       <c r="L1385" t="str">
-        <v>2.750</v>
+        <v>2.250</v>
       </c>
     </row>
     <row r="1386">
@@ -53221,16 +53221,16 @@
     </row>
     <row r="1391">
       <c r="A1391" t="str">
-        <v>D0149577</v>
+        <v>D0148403</v>
       </c>
       <c r="B1391" t="str">
-        <v>2.030</v>
+        <v>900</v>
       </c>
       <c r="C1391" t="str">
         <v>304DL</v>
       </c>
       <c r="D1391" t="str">
-        <v>1.99</v>
+        <v>1.00</v>
       </c>
       <c r="E1391" t="str">
         <v>1277.000</v>
@@ -53259,16 +53259,16 @@
     </row>
     <row r="1392">
       <c r="A1392" t="str">
-        <v>D0148403</v>
+        <v>D0149577</v>
       </c>
       <c r="B1392" t="str">
-        <v>900</v>
+        <v>2.030</v>
       </c>
       <c r="C1392" t="str">
         <v>304DL</v>
       </c>
       <c r="D1392" t="str">
-        <v>1.00</v>
+        <v>1.99</v>
       </c>
       <c r="E1392" t="str">
         <v>1277.000</v>
@@ -54057,19 +54057,19 @@
     </row>
     <row r="1413">
       <c r="A1413" t="str">
-        <v>D0149178</v>
+        <v>D0149455</v>
       </c>
       <c r="B1413" t="str">
-        <v>3.077</v>
+        <v>6.200</v>
       </c>
       <c r="C1413" t="str">
         <v>304DL</v>
       </c>
       <c r="D1413" t="str">
-        <v>0.61</v>
+        <v>1.50</v>
       </c>
       <c r="E1413" t="str">
-        <v>1277.000</v>
+        <v>1510.000</v>
       </c>
       <c r="F1413" t="str">
         <v>0.000</v>
@@ -54095,19 +54095,19 @@
     </row>
     <row r="1414">
       <c r="A1414" t="str">
-        <v>D0149455</v>
+        <v>D0149178</v>
       </c>
       <c r="B1414" t="str">
-        <v>6.200</v>
+        <v>3.077</v>
       </c>
       <c r="C1414" t="str">
         <v>304DL</v>
       </c>
       <c r="D1414" t="str">
-        <v>1.50</v>
+        <v>0.61</v>
       </c>
       <c r="E1414" t="str">
-        <v>1510.000</v>
+        <v>1277.000</v>
       </c>
       <c r="F1414" t="str">
         <v>0.000</v>
@@ -54247,28 +54247,28 @@
     </row>
     <row r="1418">
       <c r="A1418" t="str">
-        <v>D0149815</v>
+        <v>D0148852</v>
       </c>
       <c r="B1418" t="str">
-        <v>4.490</v>
+        <v>920</v>
       </c>
       <c r="C1418" t="str">
         <v>304DL</v>
       </c>
       <c r="D1418" t="str">
-        <v>3.97</v>
+        <v>1.97</v>
       </c>
       <c r="E1418" t="str">
-        <v>1277.000</v>
+        <v>1250.000</v>
       </c>
       <c r="F1418" t="str">
-        <v>0.000</v>
+        <v>2500.000</v>
       </c>
       <c r="G1418" t="str">
-        <v>COILS</v>
+        <v>BLANKS</v>
       </c>
       <c r="H1418" t="str">
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="I1418" t="str">
         <v>2</v>
@@ -54280,33 +54280,33 @@
         <v>NO</v>
       </c>
       <c r="L1418" t="str">
-        <v>2.350</v>
+        <v>2.750</v>
       </c>
     </row>
     <row r="1419">
       <c r="A1419" t="str">
-        <v>D0148852</v>
+        <v>D0149815</v>
       </c>
       <c r="B1419" t="str">
-        <v>920</v>
+        <v>4.490</v>
       </c>
       <c r="C1419" t="str">
         <v>304DL</v>
       </c>
       <c r="D1419" t="str">
-        <v>1.97</v>
+        <v>3.97</v>
       </c>
       <c r="E1419" t="str">
-        <v>1250.000</v>
+        <v>1277.000</v>
       </c>
       <c r="F1419" t="str">
-        <v>2500.000</v>
+        <v>0.000</v>
       </c>
       <c r="G1419" t="str">
-        <v>BLANKS</v>
+        <v>COILS</v>
       </c>
       <c r="H1419" t="str">
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="I1419" t="str">
         <v>2</v>
@@ -54318,7 +54318,7 @@
         <v>NO</v>
       </c>
       <c r="L1419" t="str">
-        <v>2.750</v>
+        <v>2.350</v>
       </c>
     </row>
     <row r="1420">
@@ -54475,28 +54475,28 @@
     </row>
     <row r="1424">
       <c r="A1424" t="str">
-        <v>C1027548</v>
+        <v>D0148602</v>
       </c>
       <c r="B1424" t="str">
-        <v>993</v>
+        <v>1.020</v>
       </c>
       <c r="C1424" t="str">
         <v>304DL</v>
       </c>
       <c r="D1424" t="str">
-        <v>0.80</v>
+        <v>1.00</v>
       </c>
       <c r="E1424" t="str">
-        <v>1250.000</v>
+        <v>1277.000</v>
       </c>
       <c r="F1424" t="str">
-        <v>2500.000</v>
+        <v>0.000</v>
       </c>
       <c r="G1424" t="str">
-        <v>BLANKS</v>
+        <v>COILS</v>
       </c>
       <c r="H1424" t="str">
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="I1424" t="str">
         <v>2</v>
@@ -54508,33 +54508,33 @@
         <v>NO</v>
       </c>
       <c r="L1424" t="str">
-        <v>2.750</v>
+        <v>2.150</v>
       </c>
     </row>
     <row r="1425">
       <c r="A1425" t="str">
-        <v>D0148602</v>
+        <v>C1027548</v>
       </c>
       <c r="B1425" t="str">
-        <v>1.020</v>
+        <v>993</v>
       </c>
       <c r="C1425" t="str">
         <v>304DL</v>
       </c>
       <c r="D1425" t="str">
-        <v>1.00</v>
+        <v>0.80</v>
       </c>
       <c r="E1425" t="str">
-        <v>1277.000</v>
+        <v>1250.000</v>
       </c>
       <c r="F1425" t="str">
-        <v>0.000</v>
+        <v>2500.000</v>
       </c>
       <c r="G1425" t="str">
-        <v>COILS</v>
+        <v>BLANKS</v>
       </c>
       <c r="H1425" t="str">
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="I1425" t="str">
         <v>2</v>
@@ -54546,7 +54546,7 @@
         <v>NO</v>
       </c>
       <c r="L1425" t="str">
-        <v>2.150</v>
+        <v>2.750</v>
       </c>
     </row>
     <row r="1426">
@@ -55919,16 +55919,16 @@
     </row>
     <row r="1462">
       <c r="A1462" t="str">
-        <v>C1027265</v>
+        <v>D0148818</v>
       </c>
       <c r="B1462" t="str">
-        <v>580</v>
+        <v>1.370</v>
       </c>
       <c r="C1462" t="str">
         <v>304DL</v>
       </c>
       <c r="D1462" t="str">
-        <v>3.00</v>
+        <v>1.50</v>
       </c>
       <c r="E1462" t="str">
         <v>1250.000</v>
@@ -55952,21 +55952,21 @@
         <v>NO</v>
       </c>
       <c r="L1462" t="str">
-        <v>2.650</v>
+        <v>2.750</v>
       </c>
     </row>
     <row r="1463">
       <c r="A1463" t="str">
-        <v>D0148818</v>
+        <v>C1027265</v>
       </c>
       <c r="B1463" t="str">
-        <v>1.370</v>
+        <v>580</v>
       </c>
       <c r="C1463" t="str">
         <v>304DL</v>
       </c>
       <c r="D1463" t="str">
-        <v>1.50</v>
+        <v>3.00</v>
       </c>
       <c r="E1463" t="str">
         <v>1250.000</v>
@@ -55990,7 +55990,7 @@
         <v>NO</v>
       </c>
       <c r="L1463" t="str">
-        <v>2.750</v>
+        <v>2.650</v>
       </c>
     </row>
     <row r="1464">
@@ -56489,78 +56489,78 @@
     </row>
     <row r="1477">
       <c r="A1477" t="str">
-        <v>C1028207</v>
+        <v>C0963397</v>
       </c>
       <c r="B1477" t="str">
-        <v>1.460</v>
+        <v>1.123</v>
       </c>
       <c r="C1477" t="str">
         <v>304DL</v>
       </c>
       <c r="D1477" t="str">
-        <v>1.47</v>
+        <v>3.95</v>
       </c>
       <c r="E1477" t="str">
-        <v>1250.000</v>
+        <v>100.000</v>
       </c>
       <c r="F1477" t="str">
-        <v>2500.000</v>
+        <v>0.000</v>
       </c>
       <c r="G1477" t="str">
-        <v>BLANKS</v>
+        <v>COILS</v>
       </c>
       <c r="H1477" t="str">
         <v>R</v>
       </c>
       <c r="I1477" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J1477" t="str">
         <v>2B</v>
       </c>
       <c r="K1477" t="str">
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="L1477" t="str">
-        <v>2.750</v>
+        <v>2.350</v>
       </c>
     </row>
     <row r="1478">
       <c r="A1478" t="str">
-        <v>C0963397</v>
+        <v>C1028207</v>
       </c>
       <c r="B1478" t="str">
-        <v>1.123</v>
+        <v>1.460</v>
       </c>
       <c r="C1478" t="str">
         <v>304DL</v>
       </c>
       <c r="D1478" t="str">
-        <v>3.95</v>
+        <v>1.47</v>
       </c>
       <c r="E1478" t="str">
-        <v>100.000</v>
+        <v>1250.000</v>
       </c>
       <c r="F1478" t="str">
-        <v>0.000</v>
+        <v>2500.000</v>
       </c>
       <c r="G1478" t="str">
-        <v>COILS</v>
+        <v>BLANKS</v>
       </c>
       <c r="H1478" t="str">
         <v>R</v>
       </c>
       <c r="I1478" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1478" t="str">
         <v>2B</v>
       </c>
       <c r="K1478" t="str">
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="L1478" t="str">
-        <v>2.350</v>
+        <v>2.750</v>
       </c>
     </row>
     <row r="1479">
@@ -56641,31 +56641,31 @@
     </row>
     <row r="1481">
       <c r="A1481" t="str">
-        <v>D0147716</v>
+        <v>C1025311</v>
       </c>
       <c r="B1481" t="str">
-        <v>1.175</v>
+        <v>1.523</v>
       </c>
       <c r="C1481" t="str">
         <v>304DL</v>
       </c>
       <c r="D1481" t="str">
-        <v>4.94</v>
+        <v>1.47</v>
       </c>
       <c r="E1481" t="str">
-        <v>1500.000</v>
+        <v>1250.000</v>
       </c>
       <c r="F1481" t="str">
-        <v>0.000</v>
+        <v>2498.000</v>
       </c>
       <c r="G1481" t="str">
-        <v>COILS</v>
+        <v>BLANKS</v>
       </c>
       <c r="H1481" t="str">
         <v>R</v>
       </c>
       <c r="I1481" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J1481" t="str">
         <v>2B</v>
@@ -56674,36 +56674,36 @@
         <v>NO</v>
       </c>
       <c r="L1481" t="str">
-        <v>2.250</v>
+        <v>2.550</v>
       </c>
     </row>
     <row r="1482">
       <c r="A1482" t="str">
-        <v>C1025311</v>
+        <v>D0147716</v>
       </c>
       <c r="B1482" t="str">
-        <v>1.523</v>
+        <v>1.175</v>
       </c>
       <c r="C1482" t="str">
         <v>304DL</v>
       </c>
       <c r="D1482" t="str">
-        <v>1.47</v>
+        <v>4.94</v>
       </c>
       <c r="E1482" t="str">
-        <v>1250.000</v>
+        <v>1500.000</v>
       </c>
       <c r="F1482" t="str">
-        <v>2498.000</v>
+        <v>0.000</v>
       </c>
       <c r="G1482" t="str">
-        <v>BLANKS</v>
+        <v>COILS</v>
       </c>
       <c r="H1482" t="str">
         <v>R</v>
       </c>
       <c r="I1482" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1482" t="str">
         <v>2B</v>
@@ -56712,7 +56712,7 @@
         <v>NO</v>
       </c>
       <c r="L1482" t="str">
-        <v>2.550</v>
+        <v>2.250</v>
       </c>
     </row>
     <row r="1483">
@@ -56983,19 +56983,19 @@
     </row>
     <row r="1490">
       <c r="A1490" t="str">
-        <v>D0149034</v>
+        <v>C1024197</v>
       </c>
       <c r="B1490" t="str">
-        <v>1.997</v>
+        <v>769</v>
       </c>
       <c r="C1490" t="str">
         <v>304DL</v>
       </c>
       <c r="D1490" t="str">
-        <v>1.98</v>
+        <v>1.22</v>
       </c>
       <c r="E1490" t="str">
-        <v>1277.000</v>
+        <v>185.000</v>
       </c>
       <c r="F1490" t="str">
         <v>0.000</v>
@@ -57004,10 +57004,10 @@
         <v>COILS</v>
       </c>
       <c r="H1490" t="str">
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="I1490" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J1490" t="str">
         <v>2B</v>
@@ -57016,24 +57016,24 @@
         <v>NO</v>
       </c>
       <c r="L1490" t="str">
-        <v>2.250</v>
+        <v>2.350</v>
       </c>
     </row>
     <row r="1491">
       <c r="A1491" t="str">
-        <v>C1024197</v>
+        <v>D0149034</v>
       </c>
       <c r="B1491" t="str">
-        <v>769</v>
+        <v>1.997</v>
       </c>
       <c r="C1491" t="str">
         <v>304DL</v>
       </c>
       <c r="D1491" t="str">
-        <v>1.22</v>
+        <v>1.98</v>
       </c>
       <c r="E1491" t="str">
-        <v>185.000</v>
+        <v>1277.000</v>
       </c>
       <c r="F1491" t="str">
         <v>0.000</v>
@@ -57042,10 +57042,10 @@
         <v>COILS</v>
       </c>
       <c r="H1491" t="str">
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="I1491" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1491" t="str">
         <v>2B</v>
@@ -57054,7 +57054,7 @@
         <v>NO</v>
       </c>
       <c r="L1491" t="str">
-        <v>2.350</v>
+        <v>2.250</v>
       </c>
     </row>
     <row r="1492">
@@ -59567,25 +59567,25 @@
     </row>
     <row r="1558">
       <c r="A1558" t="str">
-        <v>D0142561</v>
+        <v>D0148360</v>
       </c>
       <c r="B1558" t="str">
-        <v>985</v>
+        <v>1.680</v>
       </c>
       <c r="C1558" t="str">
         <v>304DT</v>
       </c>
       <c r="D1558" t="str">
-        <v>3.97</v>
+        <v>0.98</v>
       </c>
       <c r="E1558" t="str">
         <v>1250.000</v>
       </c>
       <c r="F1558" t="str">
-        <v>1700.000</v>
+        <v>0.000</v>
       </c>
       <c r="G1558" t="str">
-        <v>BLANKS</v>
+        <v>COILS</v>
       </c>
       <c r="H1558" t="str">
         <v>R</v>
@@ -59600,30 +59600,30 @@
         <v>NO</v>
       </c>
       <c r="L1558" t="str">
-        <v>2.450</v>
+        <v>2.250</v>
       </c>
     </row>
     <row r="1559">
       <c r="A1559" t="str">
-        <v>D0148360</v>
+        <v>D0142561</v>
       </c>
       <c r="B1559" t="str">
-        <v>1.680</v>
+        <v>985</v>
       </c>
       <c r="C1559" t="str">
         <v>304DT</v>
       </c>
       <c r="D1559" t="str">
-        <v>0.98</v>
+        <v>3.97</v>
       </c>
       <c r="E1559" t="str">
         <v>1250.000</v>
       </c>
       <c r="F1559" t="str">
-        <v>0.000</v>
+        <v>1700.000</v>
       </c>
       <c r="G1559" t="str">
-        <v>COILS</v>
+        <v>BLANKS</v>
       </c>
       <c r="H1559" t="str">
         <v>R</v>
@@ -59638,7 +59638,7 @@
         <v>NO</v>
       </c>
       <c r="L1559" t="str">
-        <v>2.250</v>
+        <v>2.450</v>
       </c>
     </row>
     <row r="1560">
@@ -60023,31 +60023,31 @@
     </row>
     <row r="1570">
       <c r="A1570" t="str">
-        <v>C1027258</v>
+        <v>C1012384</v>
       </c>
       <c r="B1570" t="str">
-        <v>830</v>
+        <v>1.510</v>
       </c>
       <c r="C1570" t="str">
         <v>304MSA</v>
       </c>
       <c r="D1570" t="str">
-        <v>1.50</v>
+        <v>0.91</v>
       </c>
       <c r="E1570" t="str">
-        <v>1000.000</v>
+        <v>400.000</v>
       </c>
       <c r="F1570" t="str">
-        <v>2000.000</v>
+        <v>0.000</v>
       </c>
       <c r="G1570" t="str">
-        <v>BLANKS</v>
+        <v>COILS</v>
       </c>
       <c r="H1570" t="str">
         <v>R</v>
       </c>
       <c r="I1570" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J1570" t="str">
         <v>2B</v>
@@ -60056,36 +60056,36 @@
         <v>NO</v>
       </c>
       <c r="L1570" t="str">
-        <v>2.750</v>
+        <v>2.350</v>
       </c>
     </row>
     <row r="1571">
       <c r="A1571" t="str">
-        <v>C1012384</v>
+        <v>C1027258</v>
       </c>
       <c r="B1571" t="str">
-        <v>1.510</v>
+        <v>830</v>
       </c>
       <c r="C1571" t="str">
         <v>304MSA</v>
       </c>
       <c r="D1571" t="str">
-        <v>0.91</v>
+        <v>1.50</v>
       </c>
       <c r="E1571" t="str">
-        <v>400.000</v>
+        <v>1000.000</v>
       </c>
       <c r="F1571" t="str">
-        <v>0.000</v>
+        <v>2000.000</v>
       </c>
       <c r="G1571" t="str">
-        <v>COILS</v>
+        <v>BLANKS</v>
       </c>
       <c r="H1571" t="str">
         <v>R</v>
       </c>
       <c r="I1571" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1571" t="str">
         <v>2B</v>
@@ -60094,7 +60094,7 @@
         <v>NO</v>
       </c>
       <c r="L1571" t="str">
-        <v>2.350</v>
+        <v>2.750</v>
       </c>
     </row>
     <row r="1572">
@@ -63139,16 +63139,16 @@
     </row>
     <row r="1652">
       <c r="A1652" t="str">
-        <v>D0148869</v>
+        <v>C1018171</v>
       </c>
       <c r="B1652" t="str">
-        <v>635</v>
+        <v>2.187</v>
       </c>
       <c r="C1652" t="str">
         <v>304PS</v>
       </c>
       <c r="D1652" t="str">
-        <v>1.00</v>
+        <v>0.91</v>
       </c>
       <c r="E1652" t="str">
         <v>260.000</v>
@@ -63163,7 +63163,7 @@
         <v>R</v>
       </c>
       <c r="I1652" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J1652" t="str">
         <v>2B</v>
@@ -63172,21 +63172,21 @@
         <v>NO</v>
       </c>
       <c r="L1652" t="str">
-        <v>2.250</v>
+        <v>2.450</v>
       </c>
     </row>
     <row r="1653">
       <c r="A1653" t="str">
-        <v>C1018171</v>
+        <v>D0148869</v>
       </c>
       <c r="B1653" t="str">
-        <v>2.187</v>
+        <v>635</v>
       </c>
       <c r="C1653" t="str">
         <v>304PS</v>
       </c>
       <c r="D1653" t="str">
-        <v>0.91</v>
+        <v>1.00</v>
       </c>
       <c r="E1653" t="str">
         <v>260.000</v>
@@ -63201,7 +63201,7 @@
         <v>R</v>
       </c>
       <c r="I1653" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1653" t="str">
         <v>2B</v>
@@ -63210,7 +63210,7 @@
         <v>NO</v>
       </c>
       <c r="L1653" t="str">
-        <v>2.450</v>
+        <v>2.250</v>
       </c>
     </row>
     <row r="1654">
@@ -64697,10 +64697,10 @@
     </row>
     <row r="1693">
       <c r="A1693" t="str">
-        <v>C1017418</v>
+        <v>C1017449</v>
       </c>
       <c r="B1693" t="str">
-        <v>961</v>
+        <v>754</v>
       </c>
       <c r="C1693" t="str">
         <v>304PSA</v>
@@ -64735,10 +64735,10 @@
     </row>
     <row r="1694">
       <c r="A1694" t="str">
-        <v>C1017449</v>
+        <v>C1017418</v>
       </c>
       <c r="B1694" t="str">
-        <v>754</v>
+        <v>961</v>
       </c>
       <c r="C1694" t="str">
         <v>304PSA</v>
@@ -70625,10 +70625,10 @@
     </row>
     <row r="1849">
       <c r="A1849" t="str">
-        <v>C1003690</v>
+        <v>C0984603</v>
       </c>
       <c r="B1849" t="str">
-        <v>680</v>
+        <v>421</v>
       </c>
       <c r="C1849" t="str">
         <v>321</v>
@@ -70663,10 +70663,10 @@
     </row>
     <row r="1850">
       <c r="A1850" t="str">
-        <v>C0984603</v>
+        <v>C1003690</v>
       </c>
       <c r="B1850" t="str">
-        <v>421</v>
+        <v>680</v>
       </c>
       <c r="C1850" t="str">
         <v>321</v>
@@ -82291,22 +82291,22 @@
     </row>
     <row r="2156">
       <c r="A2156" t="str">
-        <v>C1027831</v>
+        <v>C0844380</v>
       </c>
       <c r="B2156" t="str">
-        <v>1.296</v>
+        <v>538</v>
       </c>
       <c r="C2156" t="str">
         <v>304DL</v>
       </c>
       <c r="D2156" t="str">
-        <v>1.00</v>
+        <v>0.70</v>
       </c>
       <c r="E2156" t="str">
-        <v>1250.000</v>
+        <v>1500.000</v>
       </c>
       <c r="F2156" t="str">
-        <v>2250.000</v>
+        <v>4000.000</v>
       </c>
       <c r="G2156" t="str">
         <v>BLANKS</v>
@@ -82315,7 +82315,7 @@
         <v>R</v>
       </c>
       <c r="I2156" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2156" t="str">
         <v>SCOTCH BRITE.1F DA 2B</v>
@@ -82324,7 +82324,7 @@
         <v>YES</v>
       </c>
       <c r="L2156" t="str">
-        <v>2.450</v>
+        <v>2.750</v>
       </c>
     </row>
     <row r="2157">
@@ -82367,22 +82367,22 @@
     </row>
     <row r="2158">
       <c r="A2158" t="str">
-        <v>C0844380</v>
+        <v>C1027831</v>
       </c>
       <c r="B2158" t="str">
-        <v>538</v>
+        <v>1.296</v>
       </c>
       <c r="C2158" t="str">
         <v>304DL</v>
       </c>
       <c r="D2158" t="str">
-        <v>0.70</v>
+        <v>1.00</v>
       </c>
       <c r="E2158" t="str">
-        <v>1500.000</v>
+        <v>1250.000</v>
       </c>
       <c r="F2158" t="str">
-        <v>4000.000</v>
+        <v>2250.000</v>
       </c>
       <c r="G2158" t="str">
         <v>BLANKS</v>
@@ -82391,7 +82391,7 @@
         <v>R</v>
       </c>
       <c r="I2158" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2158" t="str">
         <v>SCOTCH BRITE.1F DA 2B</v>
@@ -82400,7 +82400,7 @@
         <v>YES</v>
       </c>
       <c r="L2158" t="str">
-        <v>2.750</v>
+        <v>2.450</v>
       </c>
     </row>
     <row r="2159">
@@ -83279,28 +83279,28 @@
     </row>
     <row r="2182">
       <c r="A2182" t="str">
-        <v>C1027355</v>
+        <v>C1027841</v>
       </c>
       <c r="B2182" t="str">
-        <v>408</v>
+        <v>365</v>
       </c>
       <c r="C2182" t="str">
         <v>304DL</v>
       </c>
       <c r="D2182" t="str">
-        <v>0.70</v>
+        <v>1.00</v>
       </c>
       <c r="E2182" t="str">
-        <v>1023.000</v>
+        <v>1500.000</v>
       </c>
       <c r="F2182" t="str">
-        <v>2000.000</v>
+        <v>2200.000</v>
       </c>
       <c r="G2182" t="str">
         <v>BLANKS</v>
       </c>
       <c r="H2182" t="str">
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="I2182" t="str">
         <v>2</v>
@@ -83309,36 +83309,36 @@
         <v>SCOTCH BRITE.1F DA 2B</v>
       </c>
       <c r="K2182" t="str">
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="L2182" t="str">
-        <v>2.450</v>
+        <v>2.350</v>
       </c>
     </row>
     <row r="2183">
       <c r="A2183" t="str">
-        <v>C1027841</v>
+        <v>C1027355</v>
       </c>
       <c r="B2183" t="str">
-        <v>365</v>
+        <v>408</v>
       </c>
       <c r="C2183" t="str">
         <v>304DL</v>
       </c>
       <c r="D2183" t="str">
-        <v>1.00</v>
+        <v>0.70</v>
       </c>
       <c r="E2183" t="str">
-        <v>1500.000</v>
+        <v>1023.000</v>
       </c>
       <c r="F2183" t="str">
-        <v>2200.000</v>
+        <v>2000.000</v>
       </c>
       <c r="G2183" t="str">
         <v>BLANKS</v>
       </c>
       <c r="H2183" t="str">
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="I2183" t="str">
         <v>2</v>
@@ -83347,10 +83347,10 @@
         <v>SCOTCH BRITE.1F DA 2B</v>
       </c>
       <c r="K2183" t="str">
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="L2183" t="str">
-        <v>2.350</v>
+        <v>2.450</v>
       </c>
     </row>
     <row r="2184">
@@ -84039,25 +84039,25 @@
     </row>
     <row r="2202">
       <c r="A2202" t="str">
-        <v>C1027459</v>
+        <v>D0149616</v>
       </c>
       <c r="B2202" t="str">
-        <v>1.239</v>
+        <v>455</v>
       </c>
       <c r="C2202" t="str">
         <v>304DL</v>
       </c>
       <c r="D2202" t="str">
-        <v>0.80</v>
+        <v>1.00</v>
       </c>
       <c r="E2202" t="str">
-        <v>1250.000</v>
+        <v>80.000</v>
       </c>
       <c r="F2202" t="str">
-        <v>1700.000</v>
+        <v>0.000</v>
       </c>
       <c r="G2202" t="str">
-        <v>BLANKS</v>
+        <v>COILS</v>
       </c>
       <c r="H2202" t="str">
         <v>R</v>
@@ -84069,33 +84069,33 @@
         <v>SCOTCH BRITE.1F DA 2B</v>
       </c>
       <c r="K2202" t="str">
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="L2202" t="str">
-        <v>2.450</v>
+        <v>2.150</v>
       </c>
     </row>
     <row r="2203">
       <c r="A2203" t="str">
-        <v>D0149616</v>
+        <v>C1027459</v>
       </c>
       <c r="B2203" t="str">
-        <v>455</v>
+        <v>1.239</v>
       </c>
       <c r="C2203" t="str">
         <v>304DL</v>
       </c>
       <c r="D2203" t="str">
-        <v>1.00</v>
+        <v>0.80</v>
       </c>
       <c r="E2203" t="str">
-        <v>80.000</v>
+        <v>1250.000</v>
       </c>
       <c r="F2203" t="str">
-        <v>0.000</v>
+        <v>1700.000</v>
       </c>
       <c r="G2203" t="str">
-        <v>COILS</v>
+        <v>BLANKS</v>
       </c>
       <c r="H2203" t="str">
         <v>R</v>
@@ -84107,10 +84107,10 @@
         <v>SCOTCH BRITE.1F DA 2B</v>
       </c>
       <c r="K2203" t="str">
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="L2203" t="str">
-        <v>2.150</v>
+        <v>2.450</v>
       </c>
     </row>
     <row r="2204">
@@ -84837,22 +84837,22 @@
     </row>
     <row r="2223">
       <c r="A2223" t="str">
-        <v>C1027325</v>
+        <v>D0148867</v>
       </c>
       <c r="B2223" t="str">
-        <v>1.043</v>
+        <v>2.252</v>
       </c>
       <c r="C2223" t="str">
         <v>304DL</v>
       </c>
       <c r="D2223" t="str">
-        <v>0.80</v>
+        <v>1.98</v>
       </c>
       <c r="E2223" t="str">
-        <v>1250.000</v>
+        <v>1500.000</v>
       </c>
       <c r="F2223" t="str">
-        <v>2000.000</v>
+        <v>3000.000</v>
       </c>
       <c r="G2223" t="str">
         <v>BLANKS</v>
@@ -84870,27 +84870,27 @@
         <v>YES</v>
       </c>
       <c r="L2223" t="str">
-        <v>2.350</v>
+        <v>2.750</v>
       </c>
     </row>
     <row r="2224">
       <c r="A2224" t="str">
-        <v>D0148867</v>
+        <v>C1027325</v>
       </c>
       <c r="B2224" t="str">
-        <v>2.252</v>
+        <v>1.043</v>
       </c>
       <c r="C2224" t="str">
         <v>304DL</v>
       </c>
       <c r="D2224" t="str">
-        <v>1.98</v>
+        <v>0.80</v>
       </c>
       <c r="E2224" t="str">
-        <v>1500.000</v>
+        <v>1250.000</v>
       </c>
       <c r="F2224" t="str">
-        <v>3000.000</v>
+        <v>2000.000</v>
       </c>
       <c r="G2224" t="str">
         <v>BLANKS</v>
@@ -84908,7 +84908,7 @@
         <v>YES</v>
       </c>
       <c r="L2224" t="str">
-        <v>2.750</v>
+        <v>2.350</v>
       </c>
     </row>
     <row r="2225">
@@ -85179,16 +85179,16 @@
     </row>
     <row r="2232">
       <c r="A2232" t="str">
-        <v>D0149075</v>
+        <v>D0148895</v>
       </c>
       <c r="B2232" t="str">
-        <v>1.141</v>
+        <v>2.035</v>
       </c>
       <c r="C2232" t="str">
         <v>304DL</v>
       </c>
       <c r="D2232" t="str">
-        <v>1.20</v>
+        <v>1.98</v>
       </c>
       <c r="E2232" t="str">
         <v>1500.000</v>
@@ -85217,16 +85217,16 @@
     </row>
     <row r="2233">
       <c r="A2233" t="str">
-        <v>D0148895</v>
+        <v>D0149075</v>
       </c>
       <c r="B2233" t="str">
-        <v>2.035</v>
+        <v>1.141</v>
       </c>
       <c r="C2233" t="str">
         <v>304DL</v>
       </c>
       <c r="D2233" t="str">
-        <v>1.98</v>
+        <v>1.20</v>
       </c>
       <c r="E2233" t="str">
         <v>1500.000</v>
@@ -85749,25 +85749,25 @@
     </row>
     <row r="2247">
       <c r="A2247" t="str">
-        <v>C1027880</v>
+        <v>D0148927</v>
       </c>
       <c r="B2247" t="str">
-        <v>1.536</v>
+        <v>948</v>
       </c>
       <c r="C2247" t="str">
         <v>304DL</v>
       </c>
       <c r="D2247" t="str">
-        <v>0.60</v>
+        <v>1.20</v>
       </c>
       <c r="E2247" t="str">
-        <v>1500.000</v>
+        <v>1000.000</v>
       </c>
       <c r="F2247" t="str">
-        <v>3000.000</v>
+        <v>0.000</v>
       </c>
       <c r="G2247" t="str">
-        <v>BLANKS</v>
+        <v>COILS</v>
       </c>
       <c r="H2247" t="str">
         <v>R</v>
@@ -85779,33 +85779,33 @@
         <v>SCOTCH BRITE.1F DA 2B</v>
       </c>
       <c r="K2247" t="str">
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="L2247" t="str">
-        <v>2.850</v>
+        <v>2.250</v>
       </c>
     </row>
     <row r="2248">
       <c r="A2248" t="str">
-        <v>D0148927</v>
+        <v>C1027880</v>
       </c>
       <c r="B2248" t="str">
-        <v>948</v>
+        <v>1.536</v>
       </c>
       <c r="C2248" t="str">
         <v>304DL</v>
       </c>
       <c r="D2248" t="str">
-        <v>1.20</v>
+        <v>0.60</v>
       </c>
       <c r="E2248" t="str">
-        <v>1000.000</v>
+        <v>1500.000</v>
       </c>
       <c r="F2248" t="str">
-        <v>0.000</v>
+        <v>3000.000</v>
       </c>
       <c r="G2248" t="str">
-        <v>COILS</v>
+        <v>BLANKS</v>
       </c>
       <c r="H2248" t="str">
         <v>R</v>
@@ -85817,10 +85817,10 @@
         <v>SCOTCH BRITE.1F DA 2B</v>
       </c>
       <c r="K2248" t="str">
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="L2248" t="str">
-        <v>2.250</v>
+        <v>2.850</v>
       </c>
     </row>
     <row r="2249">
@@ -87041,28 +87041,28 @@
     </row>
     <row r="2281">
       <c r="A2281" t="str">
-        <v>C1027535</v>
+        <v>D0148754</v>
       </c>
       <c r="B2281" t="str">
-        <v>486</v>
+        <v>3.500</v>
       </c>
       <c r="C2281" t="str">
         <v>304DL</v>
       </c>
       <c r="D2281" t="str">
-        <v>1.00</v>
+        <v>1.98</v>
       </c>
       <c r="E2281" t="str">
-        <v>1000.000</v>
+        <v>1522.000</v>
       </c>
       <c r="F2281" t="str">
-        <v>2000.000</v>
+        <v>0.000</v>
       </c>
       <c r="G2281" t="str">
-        <v>BLANKS</v>
+        <v>COILS</v>
       </c>
       <c r="H2281" t="str">
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="I2281" t="str">
         <v>2</v>
@@ -87074,33 +87074,33 @@
         <v>NO</v>
       </c>
       <c r="L2281" t="str">
-        <v>2.650</v>
+        <v>2.350</v>
       </c>
     </row>
     <row r="2282">
       <c r="A2282" t="str">
-        <v>D0148754</v>
+        <v>C1027535</v>
       </c>
       <c r="B2282" t="str">
-        <v>3.500</v>
+        <v>486</v>
       </c>
       <c r="C2282" t="str">
         <v>304DL</v>
       </c>
       <c r="D2282" t="str">
-        <v>1.98</v>
+        <v>1.00</v>
       </c>
       <c r="E2282" t="str">
-        <v>1522.000</v>
+        <v>1000.000</v>
       </c>
       <c r="F2282" t="str">
-        <v>0.000</v>
+        <v>2000.000</v>
       </c>
       <c r="G2282" t="str">
-        <v>COILS</v>
+        <v>BLANKS</v>
       </c>
       <c r="H2282" t="str">
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="I2282" t="str">
         <v>2</v>
@@ -87112,7 +87112,7 @@
         <v>NO</v>
       </c>
       <c r="L2282" t="str">
-        <v>2.350</v>
+        <v>2.650</v>
       </c>
     </row>
     <row r="2283">
@@ -88067,25 +88067,25 @@
     </row>
     <row r="2308">
       <c r="A2308" t="str">
-        <v>C1027294</v>
+        <v>D0149640</v>
       </c>
       <c r="B2308" t="str">
-        <v>388</v>
+        <v>3.391</v>
       </c>
       <c r="C2308" t="str">
         <v>304DL</v>
       </c>
       <c r="D2308" t="str">
-        <v>0.80</v>
+        <v>0.81</v>
       </c>
       <c r="E2308" t="str">
-        <v>810.000</v>
+        <v>1000.000</v>
       </c>
       <c r="F2308" t="str">
-        <v>2000.000</v>
+        <v>0.000</v>
       </c>
       <c r="G2308" t="str">
-        <v>BLANKS</v>
+        <v>COILS</v>
       </c>
       <c r="H2308" t="str">
         <v>R</v>
@@ -88100,7 +88100,7 @@
         <v>NO</v>
       </c>
       <c r="L2308" t="str">
-        <v>2.350</v>
+        <v>2.250</v>
       </c>
     </row>
     <row r="2309">
@@ -88143,25 +88143,25 @@
     </row>
     <row r="2310">
       <c r="A2310" t="str">
-        <v>D0149640</v>
+        <v>C1027294</v>
       </c>
       <c r="B2310" t="str">
-        <v>3.391</v>
+        <v>388</v>
       </c>
       <c r="C2310" t="str">
         <v>304DL</v>
       </c>
       <c r="D2310" t="str">
-        <v>0.81</v>
+        <v>0.80</v>
       </c>
       <c r="E2310" t="str">
-        <v>1000.000</v>
+        <v>810.000</v>
       </c>
       <c r="F2310" t="str">
-        <v>0.000</v>
+        <v>2000.000</v>
       </c>
       <c r="G2310" t="str">
-        <v>COILS</v>
+        <v>BLANKS</v>
       </c>
       <c r="H2310" t="str">
         <v>R</v>
@@ -88176,7 +88176,7 @@
         <v>NO</v>
       </c>
       <c r="L2310" t="str">
-        <v>2.250</v>
+        <v>2.350</v>
       </c>
     </row>
     <row r="2311">
@@ -89587,10 +89587,10 @@
     </row>
     <row r="2348">
       <c r="A2348" t="str">
-        <v>C1027444</v>
+        <v>C1027527</v>
       </c>
       <c r="B2348" t="str">
-        <v>458</v>
+        <v>404</v>
       </c>
       <c r="C2348" t="str">
         <v>441HP</v>
@@ -89602,7 +89602,7 @@
         <v>1250.000</v>
       </c>
       <c r="F2348" t="str">
-        <v>2500.000</v>
+        <v>2400.000</v>
       </c>
       <c r="G2348" t="str">
         <v>BLANKS</v>
@@ -89617,33 +89617,33 @@
         <v>DC2 (LINEN CLOTH)</v>
       </c>
       <c r="K2348" t="str">
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="L2348" t="str">
-        <v>1.950</v>
+        <v>1.650</v>
       </c>
     </row>
     <row r="2349">
       <c r="A2349" t="str">
-        <v>C1027498</v>
+        <v>C1027444</v>
       </c>
       <c r="B2349" t="str">
-        <v>864</v>
+        <v>458</v>
       </c>
       <c r="C2349" t="str">
         <v>441HP</v>
       </c>
       <c r="D2349" t="str">
-        <v>0.80</v>
+        <v>1.00</v>
       </c>
       <c r="E2349" t="str">
-        <v>200.000</v>
+        <v>1250.000</v>
       </c>
       <c r="F2349" t="str">
-        <v>0.000</v>
+        <v>2500.000</v>
       </c>
       <c r="G2349" t="str">
-        <v>COILS</v>
+        <v>BLANKS</v>
       </c>
       <c r="H2349" t="str">
         <v>R</v>
@@ -89655,33 +89655,33 @@
         <v>DC2 (LINEN CLOTH)</v>
       </c>
       <c r="K2349" t="str">
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="L2349" t="str">
-        <v>1.550</v>
+        <v>1.950</v>
       </c>
     </row>
     <row r="2350">
       <c r="A2350" t="str">
-        <v>C1027527</v>
+        <v>C1027498</v>
       </c>
       <c r="B2350" t="str">
-        <v>404</v>
+        <v>864</v>
       </c>
       <c r="C2350" t="str">
         <v>441HP</v>
       </c>
       <c r="D2350" t="str">
-        <v>1.00</v>
+        <v>0.80</v>
       </c>
       <c r="E2350" t="str">
-        <v>1250.000</v>
+        <v>200.000</v>
       </c>
       <c r="F2350" t="str">
-        <v>2400.000</v>
+        <v>0.000</v>
       </c>
       <c r="G2350" t="str">
-        <v>BLANKS</v>
+        <v>COILS</v>
       </c>
       <c r="H2350" t="str">
         <v>R</v>
@@ -89696,7 +89696,7 @@
         <v>YES</v>
       </c>
       <c r="L2350" t="str">
-        <v>1.650</v>
+        <v>1.550</v>
       </c>
     </row>
     <row r="2351">
